--- a/Datamart_Risiko_Operasional.xlsx
+++ b/Datamart_Risiko_Operasional.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\geraldom\Downloads\portal-risiko-operasional\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\02. Project\FPK MRO\00. Datamart\Datamart-Riskops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18687F0F-48F8-42C3-ADC0-1766E3B3E2B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0760C11B-B83D-4D3E-8479-376FA878CFC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PANDUAN" sheetId="2" r:id="rId1"/>
@@ -694,7 +694,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="173" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
@@ -1138,21 +1138,6 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1213,22 +1198,10 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1238,10 +1211,37 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1250,7 +1250,37 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="24">
+  <dxfs count="22">
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.89996032593768116"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.89996032593768116"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color theme="1"/>
@@ -1283,11 +1313,11 @@
     </dxf>
     <dxf>
       <font>
-        <color theme="1"/>
+        <color theme="0"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor theme="3" tint="0.89996032593768116"/>
+          <bgColor theme="3" tint="0.24994659260841701"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1353,6 +1383,16 @@
     </dxf>
     <dxf>
       <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.89996032593768116"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="0"/>
       </font>
       <fill>
@@ -1368,16 +1408,6 @@
       <fill>
         <patternFill>
           <bgColor theme="3" tint="0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.89996032593768116"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1418,56 +1448,6 @@
       <fill>
         <patternFill>
           <bgColor theme="3" tint="0.89996032593768116"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.89996032593768116"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.89996032593768116"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.24994659260841701"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1752,27 +1732,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C32"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="3" width="62" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
+    <row r="1" spans="1:3" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-    </row>
-    <row r="3" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="24" t="s">
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+    </row>
+    <row r="3" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="51" t="s">
         <v>56</v>
       </c>
-      <c r="C3" s="24"/>
-    </row>
-    <row r="4" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C3" s="51"/>
+    </row>
+    <row r="4" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>57</v>
       </c>
@@ -1780,7 +1760,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
         <v>59</v>
       </c>
@@ -1788,7 +1768,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
         <v>61</v>
       </c>
@@ -1796,7 +1776,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
         <v>63</v>
       </c>
@@ -1804,7 +1784,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
         <v>65</v>
       </c>
@@ -1812,7 +1792,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
         <v>67</v>
       </c>
@@ -1820,7 +1800,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
         <v>69</v>
       </c>
@@ -1828,13 +1808,13 @@
         <v>70</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="24" t="s">
+    <row r="12" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="51" t="s">
         <v>71</v>
       </c>
-      <c r="C12" s="24"/>
-    </row>
-    <row r="13" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C12" s="51"/>
+    </row>
+    <row r="13" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="s">
         <v>72</v>
       </c>
@@ -1842,7 +1822,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
         <v>74</v>
       </c>
@@ -1850,7 +1830,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="3" t="s">
         <v>76</v>
       </c>
@@ -1858,13 +1838,13 @@
         <v>77</v>
       </c>
     </row>
-    <row r="17" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="24" t="s">
+    <row r="17" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="51" t="s">
         <v>78</v>
       </c>
-      <c r="C17" s="24"/>
-    </row>
-    <row r="18" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C17" s="51"/>
+    </row>
+    <row r="18" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="3" t="s">
         <v>10</v>
       </c>
@@ -1872,7 +1852,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="19" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="3" t="s">
         <v>13</v>
       </c>
@@ -1880,13 +1860,13 @@
         <v>80</v>
       </c>
     </row>
-    <row r="21" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="24" t="s">
+    <row r="21" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="51" t="s">
         <v>81</v>
       </c>
-      <c r="C21" s="24"/>
-    </row>
-    <row r="22" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C21" s="51"/>
+    </row>
+    <row r="22" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="3" t="s">
         <v>82</v>
       </c>
@@ -1894,7 +1874,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="23" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="3" t="s">
         <v>84</v>
       </c>
@@ -1902,7 +1882,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="24" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="3" t="s">
         <v>86</v>
       </c>
@@ -1910,13 +1890,13 @@
         <v>87</v>
       </c>
     </row>
-    <row r="27" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="22" t="s">
+    <row r="27" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="49" t="s">
         <v>88</v>
       </c>
-      <c r="C27" s="22"/>
-    </row>
-    <row r="28" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C27" s="49"/>
+    </row>
+    <row r="28" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="6" t="s">
         <v>89</v>
       </c>
@@ -1924,7 +1904,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="29" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="6" t="s">
         <v>91</v>
       </c>
@@ -1932,7 +1912,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="30" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="6" t="s">
         <v>93</v>
       </c>
@@ -1940,7 +1920,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="31" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="6" t="s">
         <v>95</v>
       </c>
@@ -1948,7 +1928,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="32" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="6" t="s">
         <v>97</v>
       </c>
@@ -1972,8 +1952,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AD40"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AH40"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -1981,3374 +1961,3735 @@
     <col min="4" max="4" width="13" customWidth="1"/>
     <col min="5" max="5" width="28" customWidth="1"/>
     <col min="6" max="17" width="14" customWidth="1"/>
-    <col min="18" max="19" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="25" max="30" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="30" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="31" max="34" width="10.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:34" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
-      <c r="R1" s="20"/>
-      <c r="S1" s="20"/>
-      <c r="T1" s="20"/>
-      <c r="U1" s="20"/>
-      <c r="V1" s="20"/>
-      <c r="W1" s="20"/>
-      <c r="X1" s="20"/>
-      <c r="Y1" s="20"/>
-      <c r="Z1" s="20"/>
-      <c r="AA1" s="20"/>
-      <c r="AB1" s="20"/>
-      <c r="AC1" s="20"/>
-      <c r="AD1" s="20"/>
-    </row>
-    <row r="2" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="58" t="s">
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
+      <c r="M1" s="54"/>
+      <c r="N1" s="54"/>
+      <c r="O1" s="54"/>
+      <c r="P1" s="54"/>
+      <c r="Q1" s="54"/>
+      <c r="R1" s="54"/>
+      <c r="S1" s="54"/>
+      <c r="T1" s="54"/>
+      <c r="U1" s="54"/>
+      <c r="V1" s="54"/>
+      <c r="W1" s="54"/>
+      <c r="X1" s="54"/>
+      <c r="Y1" s="54"/>
+      <c r="Z1" s="54"/>
+      <c r="AA1" s="54"/>
+      <c r="AB1" s="54"/>
+      <c r="AC1" s="54"/>
+      <c r="AD1" s="54"/>
+      <c r="AE1" s="54"/>
+      <c r="AF1" s="54"/>
+      <c r="AG1" s="54"/>
+      <c r="AH1" s="54"/>
+    </row>
+    <row r="2" spans="1:34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="58" t="s">
+      <c r="C2" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="58" t="s">
+      <c r="D2" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="58" t="s">
+      <c r="E2" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="51" t="s">
+      <c r="F2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="52"/>
-      <c r="L2" s="52"/>
-      <c r="M2" s="52"/>
-      <c r="N2" s="52"/>
-      <c r="O2" s="52"/>
-      <c r="P2" s="52"/>
-      <c r="Q2" s="52"/>
-      <c r="R2" s="52"/>
-      <c r="S2" s="52"/>
-      <c r="T2" s="52"/>
-      <c r="U2" s="52"/>
-      <c r="V2" s="52"/>
-      <c r="W2" s="52"/>
-      <c r="X2" s="52"/>
-      <c r="Y2" s="52"/>
-      <c r="Z2" s="52"/>
-      <c r="AA2" s="52"/>
-      <c r="AB2" s="52"/>
-      <c r="AC2" s="52"/>
-      <c r="AD2" s="52"/>
-    </row>
-    <row r="3" spans="1:30" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="59"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="25">
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="59"/>
+      <c r="L2" s="59"/>
+      <c r="M2" s="59"/>
+      <c r="N2" s="59"/>
+      <c r="O2" s="59"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="59"/>
+      <c r="Y2" s="59"/>
+      <c r="Z2" s="59"/>
+      <c r="AA2" s="59"/>
+      <c r="AB2" s="59"/>
+      <c r="AC2" s="59"/>
+      <c r="AD2" s="59"/>
+      <c r="AE2" s="59"/>
+      <c r="AF2" s="59"/>
+      <c r="AG2" s="59"/>
+      <c r="AH2" s="59"/>
+    </row>
+    <row r="3" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="57"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="20">
         <v>202405</v>
       </c>
-      <c r="G3" s="25">
+      <c r="G3" s="20">
         <v>202406</v>
       </c>
-      <c r="H3" s="25">
+      <c r="H3" s="20">
         <v>202407</v>
       </c>
-      <c r="I3" s="25">
+      <c r="I3" s="20">
         <v>202408</v>
       </c>
-      <c r="J3" s="25">
+      <c r="J3" s="20">
         <v>202409</v>
       </c>
-      <c r="K3" s="25">
+      <c r="K3" s="20">
         <v>202410</v>
       </c>
-      <c r="L3" s="25">
+      <c r="L3" s="20">
         <v>202411</v>
       </c>
-      <c r="M3" s="25">
+      <c r="M3" s="20">
         <v>202412</v>
       </c>
-      <c r="N3" s="25">
+      <c r="N3" s="20">
         <v>202501</v>
       </c>
-      <c r="O3" s="25">
+      <c r="O3" s="20">
         <v>202502</v>
       </c>
-      <c r="P3" s="25">
+      <c r="P3" s="20">
         <v>202503</v>
       </c>
-      <c r="Q3" s="25">
+      <c r="Q3" s="20">
         <v>202504</v>
       </c>
-      <c r="R3" s="25">
+      <c r="R3" s="20">
         <v>202505</v>
       </c>
-      <c r="S3" s="25">
+      <c r="S3" s="20">
         <v>202506</v>
       </c>
-      <c r="T3" s="25">
+      <c r="T3" s="20">
         <v>202507</v>
       </c>
-      <c r="U3" s="25">
+      <c r="U3" s="20">
         <v>202508</v>
       </c>
-      <c r="V3" s="25">
+      <c r="V3" s="20">
         <v>202509</v>
       </c>
-      <c r="W3" s="25">
+      <c r="W3" s="20">
         <v>202510</v>
       </c>
-      <c r="X3" s="25">
+      <c r="X3" s="20">
         <v>202511</v>
       </c>
-      <c r="Y3" s="25">
+      <c r="Y3" s="20">
         <v>202512</v>
       </c>
-      <c r="Z3" s="44">
+      <c r="Z3" s="39">
         <v>202601</v>
       </c>
-      <c r="AA3" s="44">
+      <c r="AA3" s="39">
         <v>202602</v>
       </c>
-      <c r="AB3" s="44">
+      <c r="AB3" s="39">
         <v>202603</v>
       </c>
-      <c r="AC3" s="44">
+      <c r="AC3" s="39">
         <v>202604</v>
       </c>
-      <c r="AD3" s="44">
+      <c r="AD3" s="39">
         <v>202605</v>
       </c>
-    </row>
-    <row r="4" spans="1:30" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="53" t="s">
+      <c r="AE3" s="39">
+        <v>202606</v>
+      </c>
+      <c r="AF3" s="39">
+        <v>202607</v>
+      </c>
+      <c r="AG3" s="39">
+        <v>202608</v>
+      </c>
+      <c r="AH3" s="39">
+        <v>202609</v>
+      </c>
+    </row>
+    <row r="4" spans="1:34" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="54"/>
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="54"/>
-      <c r="K4" s="54"/>
-      <c r="L4" s="54"/>
-      <c r="M4" s="54"/>
-      <c r="N4" s="54"/>
-      <c r="O4" s="54"/>
-      <c r="P4" s="54"/>
-      <c r="Q4" s="54"/>
-    </row>
-    <row r="5" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="53"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="53"/>
+      <c r="K4" s="53"/>
+      <c r="L4" s="53"/>
+      <c r="M4" s="53"/>
+      <c r="N4" s="53"/>
+      <c r="O4" s="53"/>
+      <c r="P4" s="53"/>
+      <c r="Q4" s="53"/>
+    </row>
+    <row r="5" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="55" t="s">
+      <c r="B5" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="55" t="s">
+      <c r="C5" s="46" t="s">
         <v>174</v>
       </c>
-      <c r="D5" s="40" t="s">
+      <c r="D5" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="40"/>
-      <c r="F5" s="26">
+      <c r="E5" s="35"/>
+      <c r="F5" s="21">
         <f>F6/F7</f>
         <v>405.99921052631578</v>
       </c>
-      <c r="G5" s="26">
+      <c r="G5" s="21">
         <v>396.89002642855309</v>
       </c>
-      <c r="H5" s="26">
+      <c r="H5" s="21">
         <v>406.17340389300779</v>
       </c>
-      <c r="I5" s="26">
+      <c r="I5" s="21">
         <v>413.02200931470395</v>
       </c>
-      <c r="J5" s="26">
+      <c r="J5" s="21">
         <v>418.26524784482757</v>
       </c>
-      <c r="K5" s="26">
+      <c r="K5" s="21">
         <v>424.00144804786754</v>
       </c>
-      <c r="L5" s="26">
+      <c r="L5" s="21">
         <v>424.13292193430357</v>
       </c>
-      <c r="M5" s="26">
+      <c r="M5" s="21">
         <v>420.24594463069104</v>
       </c>
-      <c r="N5" s="26">
+      <c r="N5" s="21">
         <v>419.70911343983192</v>
       </c>
-      <c r="O5" s="26">
+      <c r="O5" s="21">
         <v>415.67255037482056</v>
       </c>
-      <c r="P5" s="26">
+      <c r="P5" s="21">
         <v>389.21530673019657</v>
       </c>
-      <c r="Q5" s="26">
+      <c r="Q5" s="21">
         <v>392.68191054361188</v>
       </c>
-      <c r="R5" s="26">
+      <c r="R5" s="21">
         <f>R6/R7</f>
         <v>393.84623885470302</v>
       </c>
-      <c r="S5" s="26">
+      <c r="S5" s="21">
         <f>S6/S7</f>
         <v>377.18352997832892</v>
       </c>
-      <c r="T5" s="26">
+      <c r="T5" s="21">
         <f>T6/T7</f>
         <v>384.56366806650459</v>
       </c>
-      <c r="U5" s="26">
+      <c r="U5" s="21">
         <f t="shared" ref="U5:W5" si="0">U6/U7</f>
         <v>389.90788295013436</v>
       </c>
-      <c r="V5" s="26">
+      <c r="V5" s="21">
         <f t="shared" si="0"/>
         <v>399.77099704051432</v>
       </c>
-      <c r="W5" s="26">
+      <c r="W5" s="21">
         <f t="shared" si="0"/>
         <v>406.88922909260748</v>
       </c>
-      <c r="X5" s="26">
+      <c r="X5" s="21">
         <v>410.41734282573418</v>
       </c>
-      <c r="Y5" s="26">
+      <c r="Y5" s="21">
         <v>403.93969642397735</v>
       </c>
-      <c r="Z5" s="26">
+      <c r="Z5" s="21">
         <v>397</v>
       </c>
-      <c r="AA5" s="26">
+      <c r="AA5" s="21">
         <v>391</v>
       </c>
-      <c r="AB5" s="26">
+      <c r="AB5" s="21">
         <v>383</v>
       </c>
-      <c r="AC5" s="26">
+      <c r="AC5" s="21">
         <v>417</v>
       </c>
-      <c r="AD5" s="26">
+      <c r="AD5" s="21">
         <v>407.72176372884877</v>
       </c>
-    </row>
-    <row r="6" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AE5" s="21">
+        <v>409</v>
+      </c>
+      <c r="AF5" s="21">
+        <v>425</v>
+      </c>
+      <c r="AG5" s="21">
+        <v>439</v>
+      </c>
+      <c r="AH5" s="21">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="6" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="55" t="s">
+      <c r="B6" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="55" t="s">
+      <c r="C6" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="40" t="s">
+      <c r="D6" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="56" t="s">
+      <c r="E6" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="26">
+      <c r="F6" s="21">
         <v>15427970</v>
       </c>
-      <c r="G6" s="26">
+      <c r="G6" s="21">
         <v>15467995</v>
       </c>
-      <c r="H6" s="26">
+      <c r="H6" s="21">
         <v>15504045</v>
       </c>
-      <c r="I6" s="26">
+      <c r="I6" s="21">
         <v>15519302</v>
       </c>
-      <c r="J6" s="26">
+      <c r="J6" s="21">
         <v>15526006</v>
       </c>
-      <c r="K6" s="26">
+      <c r="K6" s="21">
         <v>15518877</v>
       </c>
-      <c r="L6" s="26">
+      <c r="L6" s="21">
         <v>15533020</v>
       </c>
-      <c r="M6" s="26">
+      <c r="M6" s="21">
         <v>15544057</v>
       </c>
-      <c r="N6" s="26">
+      <c r="N6" s="21">
         <v>15580022</v>
       </c>
-      <c r="O6" s="26">
+      <c r="O6" s="21">
         <v>15636770</v>
       </c>
-      <c r="P6" s="26">
+      <c r="P6" s="21">
         <v>15683820</v>
       </c>
-      <c r="Q6" s="26">
+      <c r="Q6" s="21">
         <v>15653479</v>
       </c>
-      <c r="R6" s="45">
+      <c r="R6" s="40">
         <v>15680988</v>
       </c>
-      <c r="S6" s="26">
+      <c r="S6" s="21">
         <v>15664432</v>
       </c>
-      <c r="T6" s="26">
+      <c r="T6" s="21">
         <v>15659048</v>
       </c>
-      <c r="U6" s="26">
+      <c r="U6" s="21">
         <v>15669618</v>
       </c>
-      <c r="V6" s="26">
+      <c r="V6" s="21">
         <v>15669424</v>
       </c>
-      <c r="W6" s="26">
+      <c r="W6" s="21">
         <v>15681104</v>
       </c>
-      <c r="X6" s="26">
+      <c r="X6" s="21">
         <v>15680405</v>
       </c>
-      <c r="Y6" s="26">
+      <c r="Y6" s="21">
         <v>15701136</v>
       </c>
-      <c r="Z6" s="26">
+      <c r="Z6" s="21">
         <v>15721405</v>
       </c>
-      <c r="AA6" s="26">
+      <c r="AA6" s="21">
         <v>15746480</v>
       </c>
-      <c r="AB6" s="26">
+      <c r="AB6" s="21">
         <v>15768544</v>
       </c>
-      <c r="AC6" s="26">
+      <c r="AC6" s="21">
         <v>15702396</v>
       </c>
-      <c r="AD6" s="26">
+      <c r="AD6" s="21">
         <v>15710335</v>
       </c>
-    </row>
-    <row r="7" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AE6" s="21">
+        <v>15722466</v>
+      </c>
+      <c r="AF6" s="21">
+        <v>15745005</v>
+      </c>
+      <c r="AG6" s="21">
+        <v>15752766</v>
+      </c>
+      <c r="AH6" s="21">
+        <v>15758336</v>
+      </c>
+    </row>
+    <row r="7" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="55" t="s">
+      <c r="B7" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="55" t="s">
+      <c r="C7" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="40" t="s">
+      <c r="D7" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="56" t="s">
+      <c r="E7" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="26">
+      <c r="F7" s="21">
         <v>38000</v>
       </c>
-      <c r="G7" s="26">
+      <c r="G7" s="21">
         <v>38973</v>
       </c>
-      <c r="H7" s="26">
+      <c r="H7" s="21">
         <v>38171</v>
       </c>
-      <c r="I7" s="26">
+      <c r="I7" s="21">
         <v>37575</v>
       </c>
-      <c r="J7" s="26">
+      <c r="J7" s="21">
         <v>37120</v>
       </c>
-      <c r="K7" s="26">
+      <c r="K7" s="21">
         <v>36601</v>
       </c>
-      <c r="L7" s="26">
+      <c r="L7" s="21">
         <v>36623</v>
       </c>
-      <c r="M7" s="26">
+      <c r="M7" s="21">
         <v>36988</v>
       </c>
-      <c r="N7" s="26">
+      <c r="N7" s="21">
         <v>37121</v>
       </c>
-      <c r="O7" s="26">
+      <c r="O7" s="21">
         <v>37618</v>
       </c>
-      <c r="P7" s="26">
+      <c r="P7" s="21">
         <v>40296</v>
       </c>
-      <c r="Q7" s="26">
+      <c r="Q7" s="21">
         <v>39863</v>
       </c>
-      <c r="R7" s="26">
+      <c r="R7" s="21">
         <v>39815</v>
       </c>
-      <c r="S7" s="26">
+      <c r="S7" s="21">
         <v>41530</v>
       </c>
-      <c r="T7" s="26">
+      <c r="T7" s="21">
         <v>40719</v>
       </c>
-      <c r="U7" s="26">
+      <c r="U7" s="21">
         <v>40188</v>
       </c>
-      <c r="V7" s="26">
+      <c r="V7" s="21">
         <v>39196</v>
       </c>
-      <c r="W7" s="26">
+      <c r="W7" s="21">
         <v>38539</v>
       </c>
-      <c r="X7" s="26">
+      <c r="X7" s="21">
         <v>38206</v>
       </c>
-      <c r="Y7" s="26">
+      <c r="Y7" s="21">
         <v>38870</v>
       </c>
-      <c r="Z7" s="26">
+      <c r="Z7" s="21">
         <v>39647</v>
       </c>
-      <c r="AA7" s="26">
+      <c r="AA7" s="21">
         <v>40230</v>
       </c>
-      <c r="AB7" s="26">
+      <c r="AB7" s="21">
         <v>41190</v>
       </c>
-      <c r="AC7" s="26">
+      <c r="AC7" s="21">
         <v>37625</v>
       </c>
-      <c r="AD7" s="26">
+      <c r="AD7" s="21">
         <v>38532</v>
       </c>
-    </row>
-    <row r="8" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AE7" s="21">
+        <v>38427</v>
+      </c>
+      <c r="AF7" s="21">
+        <v>37011</v>
+      </c>
+      <c r="AG7" s="21">
+        <v>35879</v>
+      </c>
+      <c r="AH7" s="21">
+        <v>35618</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="55" t="s">
+      <c r="B8" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="55" t="s">
+      <c r="C8" s="46" t="s">
         <v>175</v>
       </c>
-      <c r="D8" s="40" t="s">
+      <c r="D8" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="40"/>
-      <c r="F8" s="26">
+      <c r="E8" s="35"/>
+      <c r="F8" s="21">
         <v>22.93578947368421</v>
       </c>
-      <c r="G8" s="26">
+      <c r="G8" s="21">
         <v>22.437379724424602</v>
       </c>
-      <c r="H8" s="26">
+      <c r="H8" s="21">
         <v>22.995205784496083</v>
       </c>
-      <c r="I8" s="26">
+      <c r="I8" s="21">
         <v>23.455968063872255</v>
       </c>
-      <c r="J8" s="26">
+      <c r="J8" s="21">
         <v>23.815813577586209</v>
       </c>
-      <c r="K8" s="26">
+      <c r="K8" s="21">
         <v>24.233026420043167</v>
       </c>
-      <c r="L8" s="26">
+      <c r="L8" s="21">
         <v>24.347459246921332</v>
       </c>
-      <c r="M8" s="26">
+      <c r="M8" s="21">
         <v>24.237996106845465</v>
       </c>
-      <c r="N8" s="26">
+      <c r="N8" s="21">
         <v>24.275450553595</v>
       </c>
-      <c r="O8" s="26">
+      <c r="O8" s="21">
         <v>24.081503535541497</v>
       </c>
-      <c r="P8" s="26">
+      <c r="P8" s="21">
         <v>22.55891403613262</v>
       </c>
-      <c r="Q8" s="26">
+      <c r="Q8" s="21">
         <v>22.859318164714146</v>
       </c>
-      <c r="R8" s="26">
+      <c r="R8" s="21">
         <f>R9/R10</f>
         <v>23.053145799321864</v>
       </c>
-      <c r="S8" s="26">
+      <c r="S8" s="21">
         <f>S9/S10</f>
         <v>22.236383337346496</v>
       </c>
-      <c r="T8" s="26">
+      <c r="T8" s="21">
         <f>T9/T10</f>
         <v>22.820526044352761</v>
       </c>
-      <c r="U8" s="26">
+      <c r="U8" s="21">
         <f>U9/U10</f>
         <v>23.199810888822533</v>
       </c>
-      <c r="V8" s="26">
+      <c r="V8" s="21">
         <f>V9/V10</f>
         <v>23.889197877334421</v>
       </c>
-      <c r="W8" s="26">
+      <c r="W8" s="21">
         <f t="shared" ref="W8" si="1">W9/W10</f>
         <v>24.389086380030619</v>
       </c>
-      <c r="X8" s="26">
+      <c r="X8" s="21">
         <v>24.687850075904308</v>
       </c>
-      <c r="Y8" s="26">
+      <c r="Y8" s="21">
         <v>24.340159506045794</v>
       </c>
-      <c r="Z8" s="26">
+      <c r="Z8" s="21">
         <v>24</v>
       </c>
-      <c r="AA8" s="26">
+      <c r="AA8" s="21">
         <v>23.65843897588864</v>
       </c>
-      <c r="AB8" s="26">
+      <c r="AB8" s="21">
         <v>23</v>
       </c>
-      <c r="AC8" s="26">
+      <c r="AC8" s="21">
         <v>25</v>
       </c>
-      <c r="AD8" s="26">
+      <c r="AD8" s="21">
         <v>25</v>
       </c>
-    </row>
-    <row r="9" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AE8" s="21">
+        <v>25</v>
+      </c>
+      <c r="AF8" s="21">
+        <v>26</v>
+      </c>
+      <c r="AG8" s="21">
+        <v>27</v>
+      </c>
+      <c r="AH8" s="21">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="55" t="s">
+      <c r="B9" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="55" t="s">
+      <c r="C9" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="40" t="s">
+      <c r="D9" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="56" t="s">
+      <c r="E9" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="26">
+      <c r="F9" s="21">
         <v>871560</v>
       </c>
-      <c r="G9" s="26">
+      <c r="G9" s="21">
         <v>874452</v>
       </c>
-      <c r="H9" s="26">
+      <c r="H9" s="21">
         <v>877750</v>
       </c>
-      <c r="I9" s="26">
+      <c r="I9" s="21">
         <v>881358</v>
       </c>
-      <c r="J9" s="26">
+      <c r="J9" s="21">
         <v>884043</v>
       </c>
-      <c r="K9" s="26">
+      <c r="K9" s="21">
         <v>886953</v>
       </c>
-      <c r="L9" s="26">
+      <c r="L9" s="21">
         <v>891677</v>
       </c>
-      <c r="M9" s="26">
+      <c r="M9" s="21">
         <v>896515</v>
       </c>
-      <c r="N9" s="26">
+      <c r="N9" s="21">
         <v>901129</v>
       </c>
-      <c r="O9" s="26">
+      <c r="O9" s="21">
         <v>905898</v>
       </c>
-      <c r="P9" s="26">
+      <c r="P9" s="21">
         <v>909034</v>
       </c>
-      <c r="Q9" s="26">
+      <c r="Q9" s="21">
         <v>911241</v>
       </c>
-      <c r="R9" s="45">
+      <c r="R9" s="40">
         <v>917861</v>
       </c>
-      <c r="S9" s="26">
+      <c r="S9" s="21">
         <v>923477</v>
       </c>
-      <c r="T9" s="26">
+      <c r="T9" s="21">
         <v>929229</v>
       </c>
-      <c r="U9" s="26">
+      <c r="U9" s="21">
         <v>932354</v>
       </c>
-      <c r="V9" s="26">
+      <c r="V9" s="21">
         <v>936361</v>
       </c>
-      <c r="W9" s="26">
+      <c r="W9" s="21">
         <v>939931</v>
       </c>
-      <c r="X9" s="26">
+      <c r="X9" s="21">
         <v>943224</v>
       </c>
-      <c r="Y9" s="26">
+      <c r="Y9" s="21">
         <v>946102</v>
       </c>
-      <c r="Z9" s="26">
+      <c r="Z9" s="21">
         <v>949658</v>
       </c>
-      <c r="AA9" s="26">
+      <c r="AA9" s="21">
         <v>951779</v>
       </c>
-      <c r="AB9" s="26">
+      <c r="AB9" s="21">
         <v>952676</v>
       </c>
-      <c r="AC9" s="26">
+      <c r="AC9" s="21">
         <v>954022</v>
       </c>
-      <c r="AD9" s="26">
+      <c r="AD9" s="21">
         <v>954512</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AE9" s="21">
+        <v>955703</v>
+      </c>
+      <c r="AF9" s="21">
+        <v>956713</v>
+      </c>
+      <c r="AG9" s="21">
+        <v>957101</v>
+      </c>
+      <c r="AH9" s="21">
+        <v>957286</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="55" t="s">
+      <c r="B10" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="55" t="s">
+      <c r="C10" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="40" t="s">
+      <c r="D10" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="56" t="s">
+      <c r="E10" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="26">
+      <c r="F10" s="21">
         <v>38000</v>
       </c>
-      <c r="G10" s="26">
+      <c r="G10" s="21">
         <v>38973</v>
       </c>
-      <c r="H10" s="26">
+      <c r="H10" s="21">
         <v>38171</v>
       </c>
-      <c r="I10" s="26">
+      <c r="I10" s="21">
         <v>37575</v>
       </c>
-      <c r="J10" s="26">
+      <c r="J10" s="21">
         <v>37120</v>
       </c>
-      <c r="K10" s="26">
+      <c r="K10" s="21">
         <v>36601</v>
       </c>
-      <c r="L10" s="26">
+      <c r="L10" s="21">
         <v>36623</v>
       </c>
-      <c r="M10" s="26">
+      <c r="M10" s="21">
         <v>36988</v>
       </c>
-      <c r="N10" s="26">
+      <c r="N10" s="21">
         <v>37121</v>
       </c>
-      <c r="O10" s="26">
+      <c r="O10" s="21">
         <v>37618</v>
       </c>
-      <c r="P10" s="26">
+      <c r="P10" s="21">
         <v>40296</v>
       </c>
-      <c r="Q10" s="26">
+      <c r="Q10" s="21">
         <v>39863</v>
       </c>
-      <c r="R10" s="26">
+      <c r="R10" s="21">
         <v>39815</v>
       </c>
-      <c r="S10" s="26">
+      <c r="S10" s="21">
         <v>41530</v>
       </c>
-      <c r="T10" s="26">
+      <c r="T10" s="21">
         <v>40719</v>
       </c>
-      <c r="U10" s="26">
+      <c r="U10" s="21">
         <v>40188</v>
       </c>
-      <c r="V10" s="26">
+      <c r="V10" s="21">
         <v>39196</v>
       </c>
-      <c r="W10" s="26">
+      <c r="W10" s="21">
         <v>38539</v>
       </c>
-      <c r="X10" s="26">
+      <c r="X10" s="21">
         <v>38206</v>
       </c>
-      <c r="Y10" s="26">
+      <c r="Y10" s="21">
         <v>38870</v>
       </c>
-      <c r="Z10" s="26">
+      <c r="Z10" s="21">
         <v>39647</v>
       </c>
-      <c r="AA10" s="26">
+      <c r="AA10" s="21">
         <v>40230</v>
       </c>
-      <c r="AB10" s="26">
+      <c r="AB10" s="21">
         <v>41190</v>
       </c>
-      <c r="AC10" s="26">
+      <c r="AC10" s="21">
         <v>37625</v>
       </c>
-      <c r="AD10" s="26">
+      <c r="AD10" s="21">
         <v>38532</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AE10" s="21">
+        <v>38427</v>
+      </c>
+      <c r="AF10" s="21">
+        <v>37011</v>
+      </c>
+      <c r="AG10" s="21">
+        <v>35879</v>
+      </c>
+      <c r="AH10" s="21">
+        <v>35618</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="55" t="s">
+      <c r="B11" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="55" t="s">
+      <c r="C11" s="46" t="s">
         <v>176</v>
       </c>
-      <c r="D11" s="40" t="s">
+      <c r="D11" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="E11" s="40"/>
-      <c r="F11" s="27">
+      <c r="E11" s="35"/>
+      <c r="F11" s="22">
         <v>0.43597210708538553</v>
       </c>
-      <c r="G11" s="27">
+      <c r="G11" s="22">
         <v>0.43988173455978974</v>
       </c>
-      <c r="H11" s="27">
+      <c r="H11" s="22">
         <v>0.44459037279231489</v>
       </c>
-      <c r="I11" s="27">
+      <c r="I11" s="22">
         <v>0.43662945220897487</v>
       </c>
-      <c r="J11" s="27">
+      <c r="J11" s="22">
         <v>0.42110846769245386</v>
       </c>
-      <c r="K11" s="27">
+      <c r="K11" s="22">
         <v>0.41360626128838052</v>
       </c>
-      <c r="L11" s="27">
+      <c r="L11" s="22">
         <v>0.40693556437620326</v>
       </c>
-      <c r="M11" s="27">
+      <c r="M11" s="22">
         <v>0.40584354420037955</v>
       </c>
-      <c r="N11" s="27">
+      <c r="N11" s="22">
         <v>0.40365922020920053</v>
       </c>
-      <c r="O11" s="27">
+      <c r="O11" s="22">
         <v>0.40137441773728944</v>
       </c>
-      <c r="P11" s="27">
+      <c r="P11" s="22">
         <v>0.39725775337587177</v>
       </c>
-      <c r="Q11" s="27">
+      <c r="Q11" s="22">
         <v>0.41426611796982166</v>
       </c>
-      <c r="R11" s="27">
+      <c r="R11" s="22">
         <f>R12/R13</f>
         <v>0.39734431267668413</v>
       </c>
-      <c r="S11" s="46">
+      <c r="S11" s="41">
         <f>S12/S13</f>
         <v>0.41107400123354787</v>
       </c>
-      <c r="T11" s="46">
+      <c r="T11" s="41">
         <f>T12/T13</f>
         <v>0.41582374254459731</v>
       </c>
-      <c r="U11" s="46">
+      <c r="U11" s="41">
         <f t="shared" ref="U11:W11" si="2">U12/U13</f>
         <v>0.4184321709579647</v>
       </c>
-      <c r="V11" s="46">
+      <c r="V11" s="41">
         <f t="shared" si="2"/>
         <v>0.42732026343069701</v>
       </c>
-      <c r="W11" s="46">
+      <c r="W11" s="41">
         <f t="shared" si="2"/>
         <v>0.42797338587623862</v>
       </c>
-      <c r="X11" s="27">
+      <c r="X11" s="22">
         <v>0.42770754415590345</v>
       </c>
-      <c r="Y11" s="27">
+      <c r="Y11" s="22">
         <v>0.42322749103854235</v>
       </c>
-      <c r="Z11" s="27">
+      <c r="Z11" s="22">
         <v>0.42017661438059245</v>
       </c>
-      <c r="AA11" s="27">
+      <c r="AA11" s="22">
         <v>0.41496714446222466</v>
       </c>
-      <c r="AB11" s="27">
+      <c r="AB11" s="22">
         <v>0.41312146839091357</v>
       </c>
-      <c r="AC11" s="27">
+      <c r="AC11" s="22">
         <v>0.4406883519478122</v>
       </c>
-      <c r="AD11" s="27">
+      <c r="AD11" s="22">
         <v>0.44348181415309529</v>
       </c>
-    </row>
-    <row r="12" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AE11" s="22">
+        <v>0.44096787247348845</v>
+      </c>
+      <c r="AF11" s="22">
+        <v>0.43711028581161376</v>
+      </c>
+      <c r="AG11" s="22">
+        <v>0.43756048039989787</v>
+      </c>
+      <c r="AH11" s="22">
+        <v>0.43405229319501393</v>
+      </c>
+    </row>
+    <row r="12" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="55" t="s">
+      <c r="B12" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="55" t="s">
+      <c r="C12" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="40" t="s">
+      <c r="D12" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="E12" s="56" t="s">
+      <c r="E12" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="F12" s="26">
+      <c r="F12" s="21">
         <v>18626</v>
       </c>
-      <c r="G12" s="26">
+      <c r="G12" s="21">
         <v>18746</v>
       </c>
-      <c r="H12" s="26">
+      <c r="H12" s="21">
         <v>18844</v>
       </c>
-      <c r="I12" s="26">
+      <c r="I12" s="21">
         <v>18427</v>
       </c>
-      <c r="J12" s="26">
+      <c r="J12" s="21">
         <v>17730</v>
       </c>
-      <c r="K12" s="26">
+      <c r="K12" s="21">
         <v>17404</v>
       </c>
-      <c r="L12" s="26">
+      <c r="L12" s="21">
         <v>17121</v>
       </c>
-      <c r="M12" s="26">
+      <c r="M12" s="21">
         <v>17055</v>
       </c>
-      <c r="N12" s="26">
+      <c r="N12" s="21">
         <v>16922</v>
       </c>
-      <c r="O12" s="26">
+      <c r="O12" s="21">
         <v>16860</v>
       </c>
-      <c r="P12" s="26">
+      <c r="P12" s="21">
         <v>16732</v>
       </c>
-      <c r="Q12" s="26">
+      <c r="Q12" s="21">
         <v>17516</v>
       </c>
-      <c r="R12" s="26">
+      <c r="R12" s="21">
         <v>16937</v>
       </c>
-      <c r="S12" s="26">
+      <c r="S12" s="21">
         <v>17662</v>
       </c>
-      <c r="T12" s="26">
+      <c r="T12" s="21">
         <v>17999</v>
       </c>
-      <c r="U12" s="26">
+      <c r="U12" s="21">
         <v>18223</v>
       </c>
-      <c r="V12" s="26">
+      <c r="V12" s="21">
         <v>18687</v>
       </c>
-      <c r="W12" s="26">
+      <c r="W12" s="21">
         <v>18734</v>
       </c>
-      <c r="X12" s="26">
+      <c r="X12" s="21">
         <v>18743</v>
       </c>
-      <c r="Y12" s="26">
+      <c r="Y12" s="21">
         <v>18586</v>
       </c>
-      <c r="Z12" s="26">
+      <c r="Z12" s="21">
         <v>18521</v>
       </c>
-      <c r="AA12" s="26">
+      <c r="AA12" s="21">
         <v>18282</v>
       </c>
-      <c r="AB12" s="26">
+      <c r="AB12" s="21">
         <v>18156</v>
       </c>
-      <c r="AC12" s="26">
+      <c r="AC12" s="21">
         <v>19298</v>
       </c>
-      <c r="AD12" s="26">
+      <c r="AD12" s="21">
         <v>19264</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AE12" s="21">
+        <v>18979</v>
+      </c>
+      <c r="AF12" s="21">
+        <v>18606</v>
+      </c>
+      <c r="AG12" s="21">
+        <v>18426</v>
+      </c>
+      <c r="AH12" s="21">
+        <v>18110</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="55" t="s">
+      <c r="B13" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="55" t="s">
+      <c r="C13" s="46" t="s">
         <v>177</v>
       </c>
-      <c r="D13" s="40" t="s">
+      <c r="D13" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="E13" s="56" t="s">
+      <c r="E13" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="F13" s="26">
+      <c r="F13" s="21">
         <v>42722.916666666664</v>
       </c>
-      <c r="G13" s="26">
+      <c r="G13" s="21">
         <v>42616</v>
       </c>
-      <c r="H13" s="26">
+      <c r="H13" s="21">
         <v>42385.083333333336</v>
       </c>
-      <c r="I13" s="26">
+      <c r="I13" s="21">
         <v>42202.833333333336</v>
       </c>
-      <c r="J13" s="26">
+      <c r="J13" s="21">
         <v>42103.166666666664</v>
       </c>
-      <c r="K13" s="26">
+      <c r="K13" s="21">
         <v>42078.666666666664</v>
       </c>
-      <c r="L13" s="26">
+      <c r="L13" s="21">
         <v>42073</v>
       </c>
-      <c r="M13" s="26">
+      <c r="M13" s="21">
         <v>42023.583333333336</v>
       </c>
-      <c r="N13" s="26">
+      <c r="N13" s="21">
         <v>41921.5</v>
       </c>
-      <c r="O13" s="26">
+      <c r="O13" s="21">
         <v>42005.666666666664</v>
       </c>
-      <c r="P13" s="26">
+      <c r="P13" s="21">
         <v>42118.75</v>
       </c>
-      <c r="Q13" s="26">
+      <c r="Q13" s="21">
         <v>42282</v>
       </c>
-      <c r="R13" s="26">
+      <c r="R13" s="21">
         <v>42625.5</v>
       </c>
-      <c r="S13" s="26">
+      <c r="S13" s="21">
         <v>42965.5</v>
       </c>
-      <c r="T13" s="26">
+      <c r="T13" s="21">
         <v>43285.166666666701</v>
       </c>
-      <c r="U13" s="26">
+      <c r="U13" s="21">
         <v>43550.666666666664</v>
       </c>
-      <c r="V13" s="26">
+      <c r="V13" s="21">
         <v>43730.666666666664</v>
       </c>
-      <c r="W13" s="26">
+      <c r="W13" s="21">
         <v>43773.75</v>
       </c>
-      <c r="X13" s="26">
+      <c r="X13" s="21">
         <v>43822</v>
       </c>
-      <c r="Y13" s="26">
+      <c r="Y13" s="21">
         <v>43914.916666666664</v>
       </c>
-      <c r="Z13" s="26">
+      <c r="Z13" s="21">
         <v>44079</v>
       </c>
-      <c r="AA13" s="26">
+      <c r="AA13" s="21">
         <v>44056.5</v>
       </c>
-      <c r="AB13" s="26">
+      <c r="AB13" s="21">
         <v>43948.333333333336</v>
       </c>
-      <c r="AC13" s="26">
+      <c r="AC13" s="21">
         <v>43790.583333333336</v>
       </c>
-      <c r="AD13" s="26">
+      <c r="AD13" s="21">
         <v>43438.083333333336</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AE13" s="21">
+        <v>43039.416666666664</v>
+      </c>
+      <c r="AF13" s="21">
+        <v>42565.916666666664</v>
+      </c>
+      <c r="AG13" s="21">
+        <v>42110.75</v>
+      </c>
+      <c r="AH13" s="21">
+        <v>41723.083333333336</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="55" t="s">
+      <c r="B14" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="55" t="s">
+      <c r="C14" s="46" t="s">
         <v>178</v>
       </c>
-      <c r="D14" s="40" t="s">
+      <c r="D14" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="40"/>
-      <c r="F14" s="27">
+      <c r="E14" s="35"/>
+      <c r="F14" s="22">
         <v>0.23195531242065415</v>
       </c>
-      <c r="G14" s="27">
+      <c r="G14" s="22">
         <v>0.25595319712966774</v>
       </c>
-      <c r="H14" s="27">
+      <c r="H14" s="22">
         <v>0.27975703772923721</v>
       </c>
-      <c r="I14" s="27">
+      <c r="I14" s="22">
         <v>0.29797432377098537</v>
       </c>
-      <c r="J14" s="27">
+      <c r="J14" s="22">
         <v>0.28831842532664292</v>
       </c>
-      <c r="K14" s="27">
+      <c r="K14" s="22">
         <v>0.29969720272998174</v>
       </c>
-      <c r="L14" s="27">
+      <c r="L14" s="22">
         <v>0.29362083151831952</v>
       </c>
-      <c r="M14" s="27">
+      <c r="M14" s="22">
         <v>0.28336039157721293</v>
       </c>
-      <c r="N14" s="27">
+      <c r="N14" s="22">
         <v>0.26007783243997357</v>
       </c>
-      <c r="O14" s="27">
+      <c r="O14" s="22">
         <v>0.28326299680007422</v>
       </c>
-      <c r="P14" s="27">
+      <c r="P14" s="22">
         <v>0.25338747099767983</v>
       </c>
-      <c r="Q14" s="27">
+      <c r="Q14" s="22">
         <v>0.25645688504212516</v>
       </c>
-      <c r="R14" s="27">
+      <c r="R14" s="22">
         <f>R15/R16</f>
         <v>0.31158183159447783</v>
       </c>
-      <c r="S14" s="46">
+      <c r="S14" s="41">
         <f>S15/S16</f>
         <v>0.32998871190267154</v>
       </c>
-      <c r="T14" s="46">
+      <c r="T14" s="41">
         <f>T15/T16</f>
         <v>0.35372311914410071</v>
       </c>
-      <c r="U14" s="46">
+      <c r="U14" s="41">
         <f t="shared" ref="U14:W14" si="3">U15/U16</f>
         <v>0.34780663490146074</v>
       </c>
-      <c r="V14" s="46">
+      <c r="V14" s="41">
         <f t="shared" si="3"/>
         <v>0.30675143390228732</v>
       </c>
-      <c r="W14" s="46">
+      <c r="W14" s="41">
         <f t="shared" si="3"/>
         <v>0.19917396567684967</v>
       </c>
-      <c r="X14" s="27">
+      <c r="X14" s="22">
         <v>0.25604372002004627</v>
       </c>
-      <c r="Y14" s="27">
+      <c r="Y14" s="22">
         <v>0.24354678873106508</v>
       </c>
-      <c r="Z14" s="27">
+      <c r="Z14" s="22">
         <v>0.2283839633875826</v>
       </c>
-      <c r="AA14" s="27">
+      <c r="AA14" s="22">
         <v>0.21404736903511842</v>
       </c>
-      <c r="AB14" s="27">
+      <c r="AB14" s="22">
         <v>0.16716903497440314</v>
       </c>
-      <c r="AC14" s="27">
+      <c r="AC14" s="22">
         <v>0.18667115935401574</v>
       </c>
-      <c r="AD14" s="27">
+      <c r="AD14" s="22">
         <v>0.21858151104940415</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AE14" s="22">
+        <v>0.25303107725182328</v>
+      </c>
+      <c r="AF14" s="22">
+        <v>0.28445518689421129</v>
+      </c>
+      <c r="AG14" s="22">
+        <v>0.27101755816620371</v>
+      </c>
+      <c r="AH14" s="22">
+        <v>0.26727896597095019</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="55" t="s">
+      <c r="B15" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="55" t="s">
+      <c r="C15" s="46" t="s">
         <v>179</v>
       </c>
-      <c r="D15" s="40" t="s">
+      <c r="D15" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="56" t="s">
+      <c r="E15" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="F15" s="26">
+      <c r="F15" s="21">
         <v>10049</v>
       </c>
-      <c r="G15" s="26">
+      <c r="G15" s="21">
         <v>11200</v>
       </c>
-      <c r="H15" s="26">
+      <c r="H15" s="21">
         <v>11975</v>
       </c>
-      <c r="I15" s="26">
+      <c r="I15" s="21">
         <v>12371</v>
       </c>
-      <c r="J15" s="26">
+      <c r="J15" s="21">
         <v>11894</v>
       </c>
-      <c r="K15" s="26">
+      <c r="K15" s="21">
         <v>12471</v>
       </c>
-      <c r="L15" s="26">
+      <c r="L15" s="21">
         <v>12133</v>
       </c>
-      <c r="M15" s="26">
+      <c r="M15" s="21">
         <v>11694</v>
       </c>
-      <c r="N15" s="26">
+      <c r="N15" s="21">
         <v>10626</v>
       </c>
-      <c r="O15" s="26">
+      <c r="O15" s="21">
         <v>12216</v>
       </c>
-      <c r="P15" s="26">
+      <c r="P15" s="21">
         <v>10921</v>
       </c>
-      <c r="Q15" s="26">
+      <c r="Q15" s="21">
         <v>11141</v>
       </c>
-      <c r="R15" s="26">
+      <c r="R15" s="21">
         <v>14783</v>
       </c>
-      <c r="S15" s="26">
+      <c r="S15" s="21">
         <v>15786</v>
       </c>
-      <c r="T15" s="26">
+      <c r="T15" s="21">
         <v>16498</v>
       </c>
-      <c r="U15" s="26">
+      <c r="U15" s="21">
         <v>15548</v>
       </c>
-      <c r="V15" s="26">
+      <c r="V15" s="21">
         <v>13317</v>
       </c>
-      <c r="W15" s="26">
+      <c r="W15" s="21">
         <v>8391</v>
       </c>
-      <c r="X15" s="26">
+      <c r="X15" s="21">
         <v>10729</v>
       </c>
-      <c r="Y15" s="26">
+      <c r="Y15" s="21">
         <v>10322</v>
       </c>
-      <c r="Z15" s="26">
+      <c r="Z15" s="21">
         <v>9781</v>
       </c>
-      <c r="AA15" s="26">
+      <c r="AA15" s="21">
         <v>9173</v>
       </c>
-      <c r="AB15" s="26">
+      <c r="AB15" s="21">
         <v>6988</v>
       </c>
-      <c r="AC15" s="26">
+      <c r="AC15" s="21">
         <v>7756</v>
       </c>
-      <c r="AD15" s="26">
+      <c r="AD15" s="21">
         <v>9446</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AE15" s="21">
+        <v>10894</v>
+      </c>
+      <c r="AF15" s="21">
+        <v>11651</v>
+      </c>
+      <c r="AG15" s="21">
+        <v>10635</v>
+      </c>
+      <c r="AH15" s="21">
+        <v>10360</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="55" t="s">
+      <c r="B16" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="55" t="s">
+      <c r="C16" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="40" t="s">
+      <c r="D16" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="E16" s="56" t="s">
+      <c r="E16" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="F16" s="26">
+      <c r="F16" s="21">
         <v>43323</v>
       </c>
-      <c r="G16" s="26">
+      <c r="G16" s="21">
         <v>43758</v>
       </c>
-      <c r="H16" s="26">
+      <c r="H16" s="21">
         <v>42805</v>
       </c>
-      <c r="I16" s="26">
+      <c r="I16" s="21">
         <v>41517</v>
       </c>
-      <c r="J16" s="26">
+      <c r="J16" s="21">
         <v>41253</v>
       </c>
-      <c r="K16" s="26">
+      <c r="K16" s="21">
         <v>41612</v>
       </c>
-      <c r="L16" s="26">
+      <c r="L16" s="21">
         <v>41322</v>
       </c>
-      <c r="M16" s="26">
+      <c r="M16" s="21">
         <v>41269</v>
       </c>
-      <c r="N16" s="26">
+      <c r="N16" s="21">
         <v>40857</v>
       </c>
-      <c r="O16" s="26">
+      <c r="O16" s="21">
         <v>43126</v>
       </c>
-      <c r="P16" s="26">
+      <c r="P16" s="21">
         <v>43100</v>
       </c>
-      <c r="Q16" s="26">
+      <c r="Q16" s="21">
         <v>43442</v>
       </c>
-      <c r="R16" s="26">
+      <c r="R16" s="21">
         <v>47445</v>
       </c>
-      <c r="S16" s="26">
+      <c r="S16" s="21">
         <v>47838</v>
       </c>
-      <c r="T16" s="26">
+      <c r="T16" s="21">
         <v>46641</v>
       </c>
-      <c r="U16" s="26">
+      <c r="U16" s="21">
         <v>44703</v>
       </c>
-      <c r="V16" s="26">
+      <c r="V16" s="21">
         <v>43413</v>
       </c>
-      <c r="W16" s="26">
+      <c r="W16" s="21">
         <v>42129</v>
       </c>
-      <c r="X16" s="26">
+      <c r="X16" s="21">
         <v>41903</v>
       </c>
-      <c r="Y16" s="26">
+      <c r="Y16" s="21">
         <v>42382</v>
       </c>
-      <c r="Z16" s="26">
+      <c r="Z16" s="21">
         <v>42827</v>
       </c>
-      <c r="AA16" s="26">
+      <c r="AA16" s="21">
         <v>42855</v>
       </c>
-      <c r="AB16" s="26">
+      <c r="AB16" s="21">
         <v>41802</v>
       </c>
-      <c r="AC16" s="26">
+      <c r="AC16" s="21">
         <v>41549</v>
       </c>
-      <c r="AD16" s="26">
+      <c r="AD16" s="21">
         <v>43215</v>
       </c>
-    </row>
-    <row r="17" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AE16" s="21">
+        <v>43054</v>
+      </c>
+      <c r="AF16" s="21">
+        <v>40959</v>
+      </c>
+      <c r="AG16" s="21">
+        <v>39241</v>
+      </c>
+      <c r="AH16" s="21">
+        <v>38761</v>
+      </c>
+    </row>
+    <row r="17" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>29</v>
       </c>
-      <c r="B17" s="55" t="s">
+      <c r="B17" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="55" t="s">
+      <c r="C17" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="D17" s="40" t="s">
+      <c r="D17" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="E17" s="56" t="s">
+      <c r="E17" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="F17" s="27">
+      <c r="F17" s="22">
         <v>0.43440000000000001</v>
       </c>
-      <c r="G17" s="27">
+      <c r="G17" s="22">
         <v>0.48730000000000001</v>
       </c>
-      <c r="H17" s="27">
+      <c r="H17" s="22">
         <v>0.44629999999999997</v>
       </c>
-      <c r="I17" s="27">
+      <c r="I17" s="22">
         <v>0.49765099601138507</v>
       </c>
-      <c r="J17" s="27">
+      <c r="J17" s="22">
         <v>0.40708204917384716</v>
       </c>
-      <c r="K17" s="27">
+      <c r="K17" s="22">
         <v>0.410935946828212</v>
       </c>
-      <c r="L17" s="27">
+      <c r="L17" s="22">
         <v>0.37351769362257287</v>
       </c>
-      <c r="M17" s="27">
+      <c r="M17" s="22">
         <v>0.40780571316260844</v>
       </c>
-      <c r="N17" s="27">
+      <c r="N17" s="22">
         <v>0.44684176468467501</v>
       </c>
-      <c r="O17" s="27">
+      <c r="O17" s="22">
         <v>0.47348881364759865</v>
       </c>
-      <c r="P17" s="27">
+      <c r="P17" s="22">
         <v>0.4802327466394648</v>
       </c>
-      <c r="Q17" s="27">
+      <c r="Q17" s="22">
         <v>0.44450787800815755</v>
       </c>
-      <c r="R17" s="27">
+      <c r="R17" s="22">
         <v>0.52386654189883131</v>
       </c>
-      <c r="S17" s="27">
+      <c r="S17" s="22">
         <v>0.508721808635335</v>
       </c>
-      <c r="T17" s="27">
+      <c r="T17" s="22">
         <v>0.49619998988671199</v>
       </c>
-      <c r="U17" s="27">
+      <c r="U17" s="22">
         <v>0.53696665010237432</v>
       </c>
-      <c r="V17" s="27">
+      <c r="V17" s="22">
         <v>0.53679661445356319</v>
       </c>
-      <c r="W17" s="27">
+      <c r="W17" s="22">
         <v>0.54966601737449761</v>
       </c>
-      <c r="X17" s="27">
+      <c r="X17" s="22">
         <v>0.5677089328181707</v>
       </c>
-      <c r="Y17" s="27">
+      <c r="Y17" s="22">
         <v>0.56379050123216179</v>
       </c>
-      <c r="Z17" s="27">
+      <c r="Z17" s="22">
         <v>0.56822608271199049</v>
       </c>
-      <c r="AA17" s="27">
+      <c r="AA17" s="22">
         <v>0.57554941595464904</v>
       </c>
-      <c r="AB17" s="27">
+      <c r="AB17" s="22">
         <v>0.58682202388681115</v>
       </c>
-      <c r="AC17" s="27">
+      <c r="AC17" s="22">
         <v>0.57365201810393096</v>
       </c>
-      <c r="AD17" s="27">
+      <c r="AD17" s="22">
         <v>0.56516764064527503</v>
       </c>
-    </row>
-    <row r="18" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AE17" s="22">
+        <v>0.58835171645513884</v>
+      </c>
+      <c r="AF17" s="22">
+        <v>0.58020000000000005</v>
+      </c>
+      <c r="AG17" s="22">
+        <v>0.56466339199371185</v>
+      </c>
+      <c r="AH17" s="22">
+        <v>0.54311471734229877</v>
+      </c>
+    </row>
+    <row r="18" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>31</v>
       </c>
-      <c r="B18" s="55" t="s">
+      <c r="B18" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="55" t="s">
+      <c r="C18" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="D18" s="40" t="s">
+      <c r="D18" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="E18" s="56" t="s">
+      <c r="E18" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="F18" s="27">
+      <c r="F18" s="22">
         <v>3.7900000000000003E-2</v>
       </c>
-      <c r="G18" s="27">
+      <c r="G18" s="22">
         <v>6.5600000000000006E-2</v>
       </c>
-      <c r="H18" s="27">
+      <c r="H18" s="22">
         <v>6.3600000000000004E-2</v>
       </c>
-      <c r="I18" s="27">
+      <c r="I18" s="22">
         <v>9.7204837700262933E-2</v>
       </c>
-      <c r="J18" s="27">
+      <c r="J18" s="22">
         <v>0.12578334729683052</v>
       </c>
-      <c r="K18" s="27">
+      <c r="K18" s="22">
         <v>0.18771340359463659</v>
       </c>
-      <c r="L18" s="27">
+      <c r="L18" s="22">
         <v>0.2213127840000105</v>
       </c>
-      <c r="M18" s="27">
+      <c r="M18" s="22">
         <v>0.22680206820012799</v>
       </c>
-      <c r="N18" s="27">
+      <c r="N18" s="22">
         <v>0.25128922173736068</v>
       </c>
-      <c r="O18" s="27">
+      <c r="O18" s="22">
         <v>0.27529582968445787</v>
       </c>
-      <c r="P18" s="27">
+      <c r="P18" s="22">
         <v>0.31237234033863537</v>
       </c>
-      <c r="Q18" s="27">
+      <c r="Q18" s="22">
         <v>0.29878956146864233</v>
       </c>
-      <c r="R18" s="27">
+      <c r="R18" s="22">
         <v>0.39678464933729352</v>
       </c>
-      <c r="S18" s="27">
+      <c r="S18" s="22">
         <v>0.386601297274902</v>
       </c>
-      <c r="T18" s="27">
+      <c r="T18" s="22">
         <v>0.36843359065629699</v>
       </c>
-      <c r="U18" s="27">
+      <c r="U18" s="22">
         <v>0.39323129371485122</v>
       </c>
-      <c r="V18" s="27">
+      <c r="V18" s="22">
         <v>0.40260427788665581</v>
       </c>
-      <c r="W18" s="27">
+      <c r="W18" s="22">
         <v>0.40994192957180903</v>
       </c>
-      <c r="X18" s="27">
+      <c r="X18" s="22">
         <v>0.43448240310106745</v>
       </c>
-      <c r="Y18" s="27">
+      <c r="Y18" s="22">
         <v>0.43476879778789534</v>
       </c>
-      <c r="Z18" s="27">
+      <c r="Z18" s="22">
         <v>0.42582013117153905</v>
       </c>
-      <c r="AA18" s="27">
+      <c r="AA18" s="22">
         <v>0.40991048901821914</v>
       </c>
-      <c r="AB18" s="27">
+      <c r="AB18" s="22">
         <v>0.43176634668112202</v>
       </c>
-      <c r="AC18" s="27">
+      <c r="AC18" s="22">
         <v>0.40225960931069693</v>
       </c>
-      <c r="AD18" s="27">
+      <c r="AD18" s="22">
         <v>0.42572617937292057</v>
       </c>
-    </row>
-    <row r="19" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AE18" s="22">
+        <v>0.42798379825409588</v>
+      </c>
+      <c r="AF18" s="22">
+        <v>0.4229</v>
+      </c>
+      <c r="AG18" s="22">
+        <v>0.3984136621608434</v>
+      </c>
+      <c r="AH18" s="22">
+        <v>0.44097828027850366</v>
+      </c>
+    </row>
+    <row r="19" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>33</v>
       </c>
-      <c r="B19" s="55" t="s">
+      <c r="B19" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="C19" s="55" t="s">
+      <c r="C19" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="D19" s="40" t="s">
+      <c r="D19" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="E19" s="56" t="s">
+      <c r="E19" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="F19" s="27">
+      <c r="F19" s="22">
         <v>0.83097178683385586</v>
       </c>
-      <c r="G19" s="27">
+      <c r="G19" s="22">
         <v>0.88477271023703186</v>
       </c>
-      <c r="H19" s="27">
+      <c r="H19" s="22">
         <v>0.90613664595939791</v>
       </c>
-      <c r="I19" s="27">
+      <c r="I19" s="22">
         <v>0.91133644207389453</v>
       </c>
-      <c r="J19" s="27">
+      <c r="J19" s="22">
         <v>0.91673341419712251</v>
       </c>
-      <c r="K19" s="27">
+      <c r="K19" s="22">
         <v>0.92407070008096892</v>
       </c>
-      <c r="L19" s="27">
+      <c r="L19" s="22">
         <v>0.92900388857355232</v>
       </c>
-      <c r="M19" s="27">
+      <c r="M19" s="22">
         <v>0.934109507766409</v>
       </c>
-      <c r="N19" s="27">
+      <c r="N19" s="22">
         <v>0.9357141228519702</v>
       </c>
-      <c r="O19" s="27">
+      <c r="O19" s="22">
         <v>0.94015562457024737</v>
       </c>
-      <c r="P19" s="27">
+      <c r="P19" s="22">
         <v>0.96655671732390358</v>
       </c>
-      <c r="Q19" s="27">
+      <c r="Q19" s="22">
         <v>0.96819433483018913</v>
       </c>
-      <c r="R19" s="27">
+      <c r="R19" s="22">
         <f>R20/R21</f>
         <v>0.97224148716152048</v>
       </c>
-      <c r="S19" s="27">
+      <c r="S19" s="22">
         <f>S20/S21</f>
         <v>0.97737191574077831</v>
       </c>
-      <c r="T19" s="27">
+      <c r="T19" s="22">
         <f>T20/T21</f>
         <v>0.97934422234572371</v>
       </c>
-      <c r="U19" s="27">
+      <c r="U19" s="22">
         <f t="shared" ref="U19:W19" si="4">U20/U21</f>
         <v>0.98095261030871406</v>
       </c>
-      <c r="V19" s="27">
+      <c r="V19" s="22">
         <f t="shared" si="4"/>
         <v>0.98426327066860686</v>
       </c>
-      <c r="W19" s="27">
+      <c r="W19" s="22">
         <f t="shared" si="4"/>
         <v>0.98575984597722266</v>
       </c>
-      <c r="X19" s="27">
+      <c r="X19" s="22">
         <v>0.98698725833827172</v>
       </c>
-      <c r="Y19" s="27">
+      <c r="Y19" s="22">
         <v>0.98778517486620365</v>
       </c>
-      <c r="Z19" s="27">
+      <c r="Z19" s="22">
         <v>0.98731594416729551</v>
       </c>
-      <c r="AA19" s="27">
+      <c r="AA19" s="22">
         <v>0.98629411801740008</v>
       </c>
-      <c r="AB19" s="27">
+      <c r="AB19" s="22">
         <v>0.99043202899486782</v>
       </c>
-      <c r="AC19" s="27">
+      <c r="AC19" s="22">
         <v>0.99043202899486782</v>
       </c>
-      <c r="AD19" s="27">
+      <c r="AD19" s="22">
         <v>0.99043202899486782</v>
       </c>
-    </row>
-    <row r="20" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AE19" s="22"/>
+      <c r="AF19" s="22"/>
+      <c r="AG19" s="22"/>
+      <c r="AH19" s="22"/>
+    </row>
+    <row r="20" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="55" t="s">
+      <c r="B20" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="C20" s="55" t="s">
+      <c r="C20" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="D20" s="40" t="s">
+      <c r="D20" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="E20" s="56" t="s">
+      <c r="E20" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="F20" s="26">
+      <c r="F20" s="21">
         <v>13.254</v>
       </c>
-      <c r="G20" s="26">
+      <c r="G20" s="21">
         <v>13255586</v>
       </c>
-      <c r="H20" s="26">
+      <c r="H20" s="21">
         <v>13500635</v>
       </c>
-      <c r="I20" s="26">
+      <c r="I20" s="21">
         <v>13404516</v>
       </c>
-      <c r="J20" s="26">
+      <c r="J20" s="21">
         <v>13350925</v>
       </c>
-      <c r="K20" s="26">
+      <c r="K20" s="21">
         <v>13424706</v>
       </c>
-      <c r="L20" s="26">
+      <c r="L20" s="21">
         <v>13452085</v>
       </c>
-      <c r="M20" s="26">
+      <c r="M20" s="21">
         <v>13450240</v>
       </c>
-      <c r="N20" s="26">
+      <c r="N20" s="21">
         <v>13460723</v>
       </c>
-      <c r="O20" s="26">
+      <c r="O20" s="21">
         <v>13351606</v>
       </c>
-      <c r="P20" s="26">
+      <c r="P20" s="21">
         <v>13665204</v>
       </c>
-      <c r="Q20" s="26">
+      <c r="Q20" s="21">
         <v>13539856</v>
       </c>
-      <c r="R20" s="26">
+      <c r="R20" s="21">
         <v>13439612</v>
       </c>
-      <c r="S20" s="26">
+      <c r="S20" s="21">
         <v>13164971</v>
       </c>
-      <c r="T20" s="26">
+      <c r="T20" s="21">
         <v>13077155</v>
       </c>
-      <c r="U20" s="26">
+      <c r="U20" s="21">
         <v>13075341</v>
       </c>
-      <c r="V20" s="26">
+      <c r="V20" s="21">
         <v>13112311</v>
       </c>
-      <c r="W20" s="26">
+      <c r="W20" s="21">
         <v>13100219</v>
       </c>
-      <c r="X20" s="26">
+      <c r="X20" s="21">
         <v>13089199</v>
       </c>
-      <c r="Y20" s="26">
+      <c r="Y20" s="21">
         <v>13010809</v>
       </c>
-      <c r="Z20" s="26">
+      <c r="Z20" s="21">
         <v>12923009</v>
       </c>
-      <c r="AA20" s="26">
+      <c r="AA20" s="21">
         <v>12846041</v>
       </c>
-      <c r="AB20" s="26">
+      <c r="AB20" s="21">
         <v>12758476</v>
       </c>
-      <c r="AC20" s="26"/>
-      <c r="AD20" s="26"/>
-    </row>
-    <row r="21" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AC20" s="21"/>
+      <c r="AD20" s="21"/>
+      <c r="AE20" s="21"/>
+      <c r="AF20" s="21"/>
+      <c r="AG20" s="21"/>
+      <c r="AH20" s="21"/>
+    </row>
+    <row r="21" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="55" t="s">
+      <c r="B21" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="C21" s="55" t="s">
+      <c r="C21" s="46" t="s">
         <v>38</v>
       </c>
-      <c r="D21" s="40" t="s">
+      <c r="D21" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="E21" s="56" t="s">
+      <c r="E21" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="F21" s="26">
+      <c r="F21" s="21">
         <v>15.95</v>
       </c>
-      <c r="G21" s="26">
+      <c r="G21" s="21">
         <v>14981911</v>
       </c>
-      <c r="H21" s="28">
+      <c r="H21" s="23">
         <v>14899116</v>
       </c>
-      <c r="I21" s="28">
+      <c r="I21" s="23">
         <v>14708636</v>
       </c>
-      <c r="J21" s="28">
+      <c r="J21" s="23">
         <v>14563585</v>
       </c>
-      <c r="K21" s="28">
+      <c r="K21" s="23">
         <v>14527791</v>
       </c>
-      <c r="L21" s="28">
+      <c r="L21" s="23">
         <v>14480117</v>
       </c>
-      <c r="M21" s="28">
+      <c r="M21" s="23">
         <v>14398997</v>
       </c>
-      <c r="N21" s="28">
+      <c r="N21" s="23">
         <v>14385508</v>
       </c>
-      <c r="O21" s="28">
+      <c r="O21" s="23">
         <v>14201485</v>
       </c>
-      <c r="P21" s="26">
+      <c r="P21" s="21">
         <v>14138026</v>
       </c>
-      <c r="Q21" s="26">
+      <c r="Q21" s="21">
         <v>13984647</v>
       </c>
-      <c r="R21" s="26">
+      <c r="R21" s="21">
         <v>13823327</v>
       </c>
-      <c r="S21" s="26">
+      <c r="S21" s="21">
         <v>13469766</v>
       </c>
-      <c r="T21" s="26">
+      <c r="T21" s="21">
         <v>13352971</v>
       </c>
-      <c r="U21" s="26">
+      <c r="U21" s="21">
         <v>13329228</v>
       </c>
-      <c r="V21" s="26">
+      <c r="V21" s="21">
         <v>13321955</v>
       </c>
-      <c r="W21" s="26">
+      <c r="W21" s="21">
         <v>13289463</v>
       </c>
-      <c r="X21" s="26">
+      <c r="X21" s="21">
         <v>13261771</v>
       </c>
-      <c r="Y21" s="26">
+      <c r="Y21" s="21">
         <v>13171699</v>
       </c>
-      <c r="Z21" s="26">
+      <c r="Z21" s="21">
         <v>13089031</v>
       </c>
-      <c r="AA21" s="26">
+      <c r="AA21" s="21">
         <v>13024554</v>
       </c>
-      <c r="AB21" s="26">
+      <c r="AB21" s="21">
         <v>12881728</v>
       </c>
-      <c r="AC21" s="26"/>
-      <c r="AD21" s="26"/>
-    </row>
-    <row r="22" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AC21" s="21"/>
+      <c r="AD21" s="21"/>
+      <c r="AE21" s="21"/>
+      <c r="AF21" s="21"/>
+      <c r="AG21" s="21"/>
+      <c r="AH21" s="21"/>
+    </row>
+    <row r="22" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>39</v>
       </c>
-      <c r="B22" s="55" t="s">
+      <c r="B22" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="55" t="s">
+      <c r="C22" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="D22" s="40" t="s">
+      <c r="D22" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="E22" s="40"/>
-      <c r="F22" s="27"/>
-      <c r="G22" s="29"/>
-      <c r="H22" s="30">
+      <c r="E22" s="35"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="25">
         <f t="shared" ref="H22:Q22" si="5">H23/H24</f>
         <v>0.98333672364765579</v>
       </c>
-      <c r="I22" s="30">
+      <c r="I22" s="25">
         <f t="shared" si="5"/>
         <v>0.98504807768971947</v>
       </c>
-      <c r="J22" s="30">
+      <c r="J22" s="25">
         <f t="shared" si="5"/>
         <v>0.96072390439959421</v>
       </c>
-      <c r="K22" s="30">
+      <c r="K22" s="25">
         <f t="shared" si="5"/>
         <v>0.98515744049642961</v>
       </c>
-      <c r="L22" s="30">
+      <c r="L22" s="25">
         <f t="shared" si="5"/>
         <v>0.9602810417478792</v>
       </c>
-      <c r="M22" s="30">
+      <c r="M22" s="25">
         <f t="shared" si="5"/>
         <v>0.97783277403963154</v>
       </c>
-      <c r="N22" s="30">
+      <c r="N22" s="25">
         <f t="shared" si="5"/>
         <v>0.96916932531546385</v>
       </c>
-      <c r="O22" s="30">
+      <c r="O22" s="25">
         <f t="shared" si="5"/>
         <v>0.98705708838447426</v>
       </c>
-      <c r="P22" s="31">
+      <c r="P22" s="26">
         <f t="shared" si="5"/>
         <v>0.98994102382637417</v>
       </c>
-      <c r="Q22" s="32">
+      <c r="Q22" s="27">
         <f t="shared" si="5"/>
         <v>0.98948738711382522</v>
       </c>
-      <c r="R22" s="32">
+      <c r="R22" s="27">
         <f>R23/R24</f>
         <v>0.99372645903365597</v>
       </c>
-      <c r="S22" s="32">
+      <c r="S22" s="27">
         <f>S23/S24</f>
         <v>0.99254747696763657</v>
       </c>
-      <c r="T22" s="32">
+      <c r="T22" s="27">
         <f>T23/T24</f>
         <v>0.9938577704086291</v>
       </c>
-      <c r="U22" s="32">
+      <c r="U22" s="27">
         <f t="shared" ref="U22:W22" si="6">U23/U24</f>
         <v>0.99379279108577523</v>
       </c>
-      <c r="V22" s="32">
+      <c r="V22" s="27">
         <f t="shared" si="6"/>
         <v>0.98421382729201923</v>
       </c>
-      <c r="W22" s="32">
+      <c r="W22" s="27">
         <f t="shared" si="6"/>
         <v>0.99417927298578967</v>
       </c>
-      <c r="X22" s="32">
+      <c r="X22" s="27">
         <v>0.99426031430626494</v>
       </c>
-      <c r="Y22" s="32">
+      <c r="Y22" s="27">
         <v>0.98375613921691663</v>
       </c>
-      <c r="Z22" s="32">
+      <c r="Z22" s="27">
         <v>0.99263701153668404</v>
       </c>
-      <c r="AA22" s="32"/>
-      <c r="AB22" s="32"/>
-      <c r="AC22" s="32"/>
-      <c r="AD22" s="32"/>
-    </row>
-    <row r="23" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AA22" s="27"/>
+      <c r="AB22" s="27"/>
+      <c r="AC22" s="27"/>
+      <c r="AD22" s="27"/>
+      <c r="AE22" s="27"/>
+      <c r="AF22" s="27"/>
+      <c r="AG22" s="27"/>
+      <c r="AH22" s="27"/>
+    </row>
+    <row r="23" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>41</v>
       </c>
-      <c r="B23" s="55" t="s">
+      <c r="B23" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="55" t="s">
+      <c r="C23" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="D23" s="40" t="s">
+      <c r="D23" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="E23" s="56" t="s">
+      <c r="E23" s="47" t="s">
         <v>43</v>
       </c>
-      <c r="F23" s="26"/>
-      <c r="G23" s="33"/>
-      <c r="H23" s="34">
+      <c r="F23" s="21"/>
+      <c r="G23" s="28"/>
+      <c r="H23" s="29">
         <v>1382538</v>
       </c>
-      <c r="I23" s="34">
+      <c r="I23" s="29">
         <v>1235467</v>
       </c>
-      <c r="J23" s="34">
+      <c r="J23" s="29">
         <v>1184660</v>
       </c>
-      <c r="K23" s="34">
+      <c r="K23" s="29">
         <v>3868001</v>
       </c>
-      <c r="L23" s="34">
+      <c r="L23" s="29">
         <v>1034626</v>
       </c>
-      <c r="M23" s="34">
+      <c r="M23" s="29">
         <v>1141080</v>
       </c>
-      <c r="N23" s="35">
+      <c r="N23" s="30">
         <v>1071124</v>
       </c>
-      <c r="O23" s="35">
+      <c r="O23" s="30">
         <v>1234764</v>
       </c>
-      <c r="P23" s="36">
+      <c r="P23" s="31">
         <v>1258908</v>
       </c>
-      <c r="Q23" s="35">
+      <c r="Q23" s="30">
         <v>703858</v>
       </c>
-      <c r="R23" s="35">
+      <c r="R23" s="30">
         <v>981444</v>
       </c>
-      <c r="S23" s="35">
+      <c r="S23" s="30">
         <v>966374</v>
       </c>
-      <c r="T23" s="35">
+      <c r="T23" s="30">
         <v>1099319</v>
       </c>
-      <c r="U23" s="35">
+      <c r="U23" s="30">
         <v>980791</v>
       </c>
-      <c r="V23" s="35">
+      <c r="V23" s="30">
         <v>1145556</v>
       </c>
-      <c r="W23" s="35">
+      <c r="W23" s="30">
         <v>1103367</v>
       </c>
-      <c r="X23" s="47">
+      <c r="X23" s="42">
         <v>960709</v>
       </c>
-      <c r="Y23" s="26">
+      <c r="Y23" s="21">
         <v>1042570</v>
       </c>
-      <c r="Z23" s="26">
+      <c r="Z23" s="21">
         <v>693755</v>
       </c>
-      <c r="AA23" s="26"/>
-      <c r="AB23" s="26"/>
-      <c r="AC23" s="26"/>
-      <c r="AD23" s="26"/>
-    </row>
-    <row r="24" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AA23" s="21"/>
+      <c r="AB23" s="21"/>
+      <c r="AC23" s="21"/>
+      <c r="AD23" s="21"/>
+      <c r="AE23" s="21"/>
+      <c r="AF23" s="21"/>
+      <c r="AG23" s="21"/>
+      <c r="AH23" s="21"/>
+    </row>
+    <row r="24" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="55" t="s">
+      <c r="B24" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="C24" s="55" t="s">
+      <c r="C24" s="46" t="s">
         <v>45</v>
       </c>
-      <c r="D24" s="40" t="s">
+      <c r="D24" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="E24" s="56" t="s">
+      <c r="E24" s="47" t="s">
         <v>43</v>
       </c>
-      <c r="F24" s="26"/>
-      <c r="G24" s="33"/>
-      <c r="H24" s="34">
+      <c r="F24" s="21"/>
+      <c r="G24" s="28"/>
+      <c r="H24" s="29">
         <v>1405966</v>
       </c>
-      <c r="I24" s="34">
+      <c r="I24" s="29">
         <v>1254220</v>
       </c>
-      <c r="J24" s="34">
+      <c r="J24" s="29">
         <v>1233091</v>
       </c>
-      <c r="K24" s="34">
+      <c r="K24" s="29">
         <v>3926277</v>
       </c>
-      <c r="L24" s="34">
+      <c r="L24" s="29">
         <v>1077420</v>
       </c>
-      <c r="M24" s="34">
+      <c r="M24" s="29">
         <v>1166948</v>
       </c>
-      <c r="N24" s="35">
+      <c r="N24" s="30">
         <v>1105198</v>
       </c>
-      <c r="O24" s="35">
+      <c r="O24" s="30">
         <v>1250955</v>
       </c>
-      <c r="P24" s="36">
+      <c r="P24" s="31">
         <v>1271700</v>
       </c>
-      <c r="Q24" s="35">
+      <c r="Q24" s="30">
         <v>711336</v>
       </c>
-      <c r="R24" s="35">
+      <c r="R24" s="30">
         <v>987640</v>
       </c>
-      <c r="S24" s="35">
+      <c r="S24" s="30">
         <v>973630</v>
       </c>
-      <c r="T24" s="35">
+      <c r="T24" s="30">
         <v>1106113</v>
       </c>
-      <c r="U24" s="35">
+      <c r="U24" s="30">
         <v>986917</v>
       </c>
-      <c r="V24" s="35">
+      <c r="V24" s="30">
         <v>1163930</v>
       </c>
-      <c r="W24" s="35">
+      <c r="W24" s="30">
         <v>1109827</v>
       </c>
-      <c r="X24" s="47">
+      <c r="X24" s="42">
         <v>966255</v>
       </c>
-      <c r="Y24" s="26">
+      <c r="Y24" s="21">
         <v>1059785</v>
       </c>
-      <c r="Z24" s="26">
+      <c r="Z24" s="21">
         <v>698901</v>
       </c>
-      <c r="AA24" s="26"/>
-      <c r="AB24" s="26"/>
-      <c r="AC24" s="26"/>
-      <c r="AD24" s="26"/>
-    </row>
-    <row r="25" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AA24" s="21"/>
+      <c r="AB24" s="21"/>
+      <c r="AC24" s="21"/>
+      <c r="AD24" s="21"/>
+      <c r="AE24" s="21"/>
+      <c r="AF24" s="21"/>
+      <c r="AG24" s="21"/>
+      <c r="AH24" s="21"/>
+    </row>
+    <row r="25" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>46</v>
       </c>
-      <c r="B25" s="55" t="s">
+      <c r="B25" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="C25" s="55" t="s">
+      <c r="C25" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="D25" s="40" t="s">
+      <c r="D25" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="E25" s="40"/>
-      <c r="F25" s="27">
+      <c r="E25" s="35"/>
+      <c r="F25" s="22">
         <v>9.5866294409514649E-2</v>
       </c>
-      <c r="G25" s="27">
+      <c r="G25" s="22">
         <v>7.6357535919638814E-2</v>
       </c>
-      <c r="H25" s="37">
+      <c r="H25" s="32">
         <v>7.6235830247792652E-2</v>
       </c>
-      <c r="I25" s="37">
+      <c r="I25" s="32">
         <v>7.2228311310500393E-2</v>
       </c>
-      <c r="J25" s="37">
+      <c r="J25" s="32">
         <v>6.9588244010755126E-2</v>
       </c>
-      <c r="K25" s="37">
+      <c r="K25" s="32">
         <v>6.7834485029082708E-2</v>
       </c>
-      <c r="L25" s="37">
+      <c r="L25" s="32">
         <v>6.3308799038216748E-2</v>
       </c>
-      <c r="M25" s="37">
+      <c r="M25" s="32">
         <v>6.1011806829779761E-2</v>
       </c>
-      <c r="N25" s="37">
+      <c r="N25" s="32">
         <v>5.8907215282162709E-2</v>
       </c>
-      <c r="O25" s="37">
+      <c r="O25" s="32">
         <v>5.9016578025340605E-2</v>
       </c>
-      <c r="P25" s="37">
+      <c r="P25" s="32">
         <v>5.8968091402521801E-2</v>
       </c>
-      <c r="Q25" s="37">
+      <c r="Q25" s="32">
         <v>5.548038334534991E-2</v>
       </c>
-      <c r="R25" s="37">
+      <c r="R25" s="32">
         <f>R26/R27</f>
         <v>4.8074817428782793E-2</v>
       </c>
-      <c r="S25" s="37">
+      <c r="S25" s="32">
         <f>S26/S27</f>
         <v>4.5930759509982384E-2</v>
       </c>
-      <c r="T25" s="37">
+      <c r="T25" s="32">
         <f>T26/T27</f>
         <v>4.4769373319171052E-2</v>
       </c>
-      <c r="U25" s="37">
+      <c r="U25" s="32">
         <f t="shared" ref="U25:W25" si="7">U26/U27</f>
         <v>4.3532821224556338E-2</v>
       </c>
-      <c r="V25" s="37">
+      <c r="V25" s="32">
         <f t="shared" si="7"/>
         <v>4.2844586649807073E-2</v>
       </c>
-      <c r="W25" s="37">
+      <c r="W25" s="32">
         <f t="shared" si="7"/>
         <v>4.0788100403114695E-2</v>
       </c>
-      <c r="X25" s="37">
+      <c r="X25" s="32">
         <v>3.9415875762279159E-2</v>
       </c>
-      <c r="Y25" s="32">
+      <c r="Y25" s="27">
         <v>3.8371127003219527E-2</v>
       </c>
-      <c r="Z25" s="32">
+      <c r="Z25" s="27">
         <v>3.9575299739485162E-2</v>
       </c>
-      <c r="AA25" s="32">
+      <c r="AA25" s="27">
         <v>4.0581899789762121E-2</v>
       </c>
-      <c r="AB25" s="32">
+      <c r="AB25" s="27">
         <v>4.0143882324663094E-2</v>
       </c>
-      <c r="AC25" s="32">
+      <c r="AC25" s="27">
         <v>3.8964510252384114E-2</v>
       </c>
-      <c r="AD25" s="32">
+      <c r="AD25" s="27">
         <v>3.5981737264696514E-2</v>
       </c>
-    </row>
-    <row r="26" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AE25" s="27">
+        <v>3.6412986042735032E-2</v>
+      </c>
+      <c r="AF25" s="27">
+        <v>3.8896722423548129E-2</v>
+      </c>
+      <c r="AG25" s="27">
+        <v>3.6797579356828591E-2</v>
+      </c>
+      <c r="AH25" s="27">
+        <v>3.5829417749763393E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>48</v>
       </c>
-      <c r="B26" s="55" t="s">
+      <c r="B26" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="55" t="s">
+      <c r="C26" s="46" t="s">
         <v>180</v>
       </c>
-      <c r="D26" s="40" t="s">
+      <c r="D26" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="E26" s="56" t="s">
+      <c r="E26" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="F26" s="26">
+      <c r="F26" s="21">
         <v>82443</v>
       </c>
-      <c r="G26" s="26">
+      <c r="G26" s="21">
         <v>66771</v>
       </c>
-      <c r="H26" s="26">
+      <c r="H26" s="21">
         <v>66916</v>
       </c>
-      <c r="I26" s="26">
+      <c r="I26" s="21">
         <v>63659</v>
       </c>
-      <c r="J26" s="26">
+      <c r="J26" s="21">
         <v>61519</v>
       </c>
-      <c r="K26" s="26">
+      <c r="K26" s="21">
         <v>60166</v>
       </c>
-      <c r="L26" s="26">
+      <c r="L26" s="21">
         <v>56451</v>
       </c>
-      <c r="M26" s="26">
+      <c r="M26" s="21">
         <v>54698</v>
       </c>
-      <c r="N26" s="26">
+      <c r="N26" s="21">
         <v>53083</v>
       </c>
-      <c r="O26" s="26">
+      <c r="O26" s="21">
         <v>53463</v>
       </c>
-      <c r="P26" s="26">
+      <c r="P26" s="21">
         <v>53604</v>
       </c>
-      <c r="Q26" s="26">
+      <c r="Q26" s="21">
         <v>50556</v>
       </c>
-      <c r="R26" s="26">
+      <c r="R26" s="21">
         <v>44126</v>
       </c>
-      <c r="S26" s="26">
+      <c r="S26" s="21">
         <v>42416</v>
       </c>
-      <c r="T26" s="26">
+      <c r="T26" s="21">
         <v>41601</v>
       </c>
-      <c r="U26" s="26">
+      <c r="U26" s="21">
         <v>40588</v>
       </c>
-      <c r="V26" s="26">
+      <c r="V26" s="21">
         <v>40118</v>
       </c>
-      <c r="W26" s="26">
+      <c r="W26" s="21">
         <v>38338</v>
       </c>
-      <c r="X26" s="26">
+      <c r="X26" s="21">
         <v>37178</v>
       </c>
-      <c r="Y26" s="26">
+      <c r="Y26" s="21">
         <v>36303</v>
       </c>
-      <c r="Z26" s="26">
+      <c r="Z26" s="21">
         <v>37583</v>
       </c>
-      <c r="AA26" s="26">
+      <c r="AA26" s="21">
         <v>38625</v>
       </c>
-      <c r="AB26" s="26">
+      <c r="AB26" s="21">
         <v>38246</v>
       </c>
-      <c r="AC26" s="26">
+      <c r="AC26" s="21">
         <v>37173</v>
       </c>
-      <c r="AD26" s="26">
+      <c r="AD26" s="21">
         <v>34345</v>
       </c>
-    </row>
-    <row r="27" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AE26" s="21">
+        <v>34800</v>
+      </c>
+      <c r="AF26" s="21">
+        <v>37213</v>
+      </c>
+      <c r="AG26" s="21">
+        <v>35219</v>
+      </c>
+      <c r="AH26" s="21">
+        <v>34299</v>
+      </c>
+    </row>
+    <row r="27" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>49</v>
       </c>
-      <c r="B27" s="55" t="s">
+      <c r="B27" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="C27" s="55" t="s">
+      <c r="C27" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="D27" s="40" t="s">
+      <c r="D27" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="E27" s="56" t="s">
+      <c r="E27" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="F27" s="26">
+      <c r="F27" s="21">
         <v>859979</v>
       </c>
-      <c r="G27" s="26">
+      <c r="G27" s="21">
         <v>874452</v>
       </c>
-      <c r="H27" s="26">
+      <c r="H27" s="21">
         <v>877750</v>
       </c>
-      <c r="I27" s="26">
+      <c r="I27" s="21">
         <v>881358</v>
       </c>
-      <c r="J27" s="26">
+      <c r="J27" s="21">
         <v>884043</v>
       </c>
-      <c r="K27" s="26">
+      <c r="K27" s="21">
         <v>886953</v>
       </c>
-      <c r="L27" s="26">
+      <c r="L27" s="21">
         <v>891677</v>
       </c>
-      <c r="M27" s="26">
+      <c r="M27" s="21">
         <v>896515</v>
       </c>
-      <c r="N27" s="26">
+      <c r="N27" s="21">
         <v>901129</v>
       </c>
-      <c r="O27" s="26">
+      <c r="O27" s="21">
         <v>905898</v>
       </c>
-      <c r="P27" s="26">
+      <c r="P27" s="21">
         <v>909034</v>
       </c>
-      <c r="Q27" s="26">
+      <c r="Q27" s="21">
         <v>911241</v>
       </c>
-      <c r="R27" s="26">
+      <c r="R27" s="21">
         <v>917861</v>
       </c>
-      <c r="S27" s="26">
+      <c r="S27" s="21">
         <v>923477</v>
       </c>
-      <c r="T27" s="26">
+      <c r="T27" s="21">
         <v>929229</v>
       </c>
-      <c r="U27" s="26">
+      <c r="U27" s="21">
         <v>932354</v>
       </c>
-      <c r="V27" s="26">
+      <c r="V27" s="21">
         <v>936361</v>
       </c>
-      <c r="W27" s="26">
+      <c r="W27" s="21">
         <v>939931</v>
       </c>
-      <c r="X27" s="26">
+      <c r="X27" s="21">
         <v>943224</v>
       </c>
-      <c r="Y27" s="26">
+      <c r="Y27" s="21">
         <v>946102</v>
       </c>
-      <c r="Z27" s="26">
+      <c r="Z27" s="21">
         <v>949658</v>
       </c>
-      <c r="AA27" s="26">
+      <c r="AA27" s="21">
         <v>951779</v>
       </c>
-      <c r="AB27" s="26">
+      <c r="AB27" s="21">
         <v>952723</v>
       </c>
-      <c r="AC27" s="26">
+      <c r="AC27" s="21">
         <v>954022</v>
       </c>
-      <c r="AD27" s="26">
+      <c r="AD27" s="21">
         <v>954512</v>
       </c>
-    </row>
-    <row r="28" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AE27" s="21">
+        <v>955703</v>
+      </c>
+      <c r="AF27" s="21">
+        <v>956713</v>
+      </c>
+      <c r="AG27" s="21">
+        <v>957101</v>
+      </c>
+      <c r="AH27" s="21">
+        <v>957286</v>
+      </c>
+    </row>
+    <row r="28" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>51</v>
       </c>
-      <c r="B28" s="55" t="s">
+      <c r="B28" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="C28" s="55" t="s">
+      <c r="C28" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="D28" s="40" t="s">
+      <c r="D28" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="E28" s="40"/>
-      <c r="F28" s="27">
+      <c r="E28" s="35"/>
+      <c r="F28" s="22">
         <v>0.21773367192372806</v>
       </c>
-      <c r="G28" s="27">
+      <c r="G28" s="22">
         <v>0.23747237436340923</v>
       </c>
-      <c r="H28" s="27">
+      <c r="H28" s="22">
         <v>0.24012867227291229</v>
       </c>
-      <c r="I28" s="27">
+      <c r="I28" s="22">
         <v>0.44283310387027691</v>
       </c>
-      <c r="J28" s="27">
+      <c r="J28" s="22">
         <v>0.55059744450743531</v>
       </c>
-      <c r="K28" s="27">
+      <c r="K28" s="22">
         <v>0.58028916740400793</v>
       </c>
-      <c r="L28" s="27">
+      <c r="L28" s="22">
         <v>0.75232878474418208</v>
       </c>
-      <c r="M28" s="27">
+      <c r="M28" s="22">
         <v>0.80368948264737305</v>
       </c>
-      <c r="N28" s="27">
+      <c r="N28" s="22">
         <v>0.78595944187715916</v>
       </c>
-      <c r="O28" s="27">
+      <c r="O28" s="22">
         <v>0.87889423719748627</v>
       </c>
-      <c r="P28" s="27">
+      <c r="P28" s="22">
         <v>0.96110093982668132</v>
       </c>
-      <c r="Q28" s="27">
+      <c r="Q28" s="22">
         <v>0.97086501543326054</v>
       </c>
-      <c r="R28" s="27">
+      <c r="R28" s="22">
         <f>R29/R30</f>
         <v>0.97948358579052341</v>
       </c>
-      <c r="S28" s="27">
+      <c r="S28" s="22">
         <f>S29/S30</f>
         <v>0.83839540909950283</v>
       </c>
-      <c r="T28" s="27">
+      <c r="T28" s="22">
         <f>T29/T30</f>
         <v>0.95458213032362171</v>
       </c>
-      <c r="U28" s="27">
+      <c r="U28" s="22">
         <f t="shared" ref="U28:W28" si="8">U29/U30</f>
         <v>0.9637603567827181</v>
       </c>
-      <c r="V28" s="27">
+      <c r="V28" s="22">
         <f t="shared" si="8"/>
         <v>0.96694541985507543</v>
       </c>
-      <c r="W28" s="27">
+      <c r="W28" s="22">
         <f t="shared" si="8"/>
         <v>0.96176543848556262</v>
       </c>
-      <c r="X28" s="27">
+      <c r="X28" s="22">
         <v>0.97875806688949152</v>
       </c>
-      <c r="Y28" s="27">
+      <c r="Y28" s="22">
         <v>0.94505984986812741</v>
       </c>
-      <c r="Z28" s="27">
+      <c r="Z28" s="22">
         <v>0.96831118355065193</v>
       </c>
-      <c r="AA28" s="27">
+      <c r="AA28" s="22">
         <v>0.98361728534356307</v>
       </c>
-      <c r="AB28" s="27">
+      <c r="AB28" s="22">
         <v>0.97145662263477328</v>
       </c>
-      <c r="AC28" s="27">
+      <c r="AC28" s="22">
         <v>0.9275180927195098</v>
       </c>
-      <c r="AD28" s="27">
+      <c r="AD28" s="22">
         <v>0.97382065542531737</v>
       </c>
-    </row>
-    <row r="29" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AE28" s="22">
+        <v>0.96004462876028884</v>
+      </c>
+      <c r="AF28" s="22">
+        <v>0.96826134652213525</v>
+      </c>
+      <c r="AG28" s="22">
+        <v>0.96008497194836318</v>
+      </c>
+      <c r="AH28" s="22">
+        <v>0.9670180896416638</v>
+      </c>
+    </row>
+    <row r="29" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>53</v>
       </c>
-      <c r="B29" s="55" t="s">
+      <c r="B29" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="C29" s="55" t="s">
+      <c r="C29" s="46" t="s">
         <v>54</v>
       </c>
-      <c r="D29" s="40" t="s">
+      <c r="D29" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="E29" s="56" t="s">
+      <c r="E29" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="F29" s="26">
+      <c r="F29" s="21">
         <v>19549</v>
       </c>
-      <c r="G29" s="26">
+      <c r="G29" s="21">
         <v>19771</v>
       </c>
-      <c r="H29" s="26">
+      <c r="H29" s="21">
         <v>24186</v>
       </c>
-      <c r="I29" s="26">
+      <c r="I29" s="21">
         <v>43422</v>
       </c>
-      <c r="J29" s="26">
+      <c r="J29" s="21">
         <v>50503</v>
       </c>
-      <c r="K29" s="26">
+      <c r="K29" s="21">
         <v>59681</v>
       </c>
-      <c r="L29" s="26">
+      <c r="L29" s="21">
         <v>70184</v>
       </c>
-      <c r="M29" s="26">
+      <c r="M29" s="21">
         <v>75980</v>
       </c>
-      <c r="N29" s="26">
+      <c r="N29" s="21">
         <v>70073</v>
       </c>
-      <c r="O29" s="26">
+      <c r="O29" s="21">
         <v>78879</v>
       </c>
-      <c r="P29" s="26">
+      <c r="P29" s="21">
         <v>78743</v>
       </c>
-      <c r="Q29" s="26">
+      <c r="Q29" s="21">
         <v>64480</v>
       </c>
-      <c r="R29" s="26">
+      <c r="R29" s="21">
         <v>90852</v>
       </c>
-      <c r="S29" s="26">
+      <c r="S29" s="21">
         <v>75386</v>
       </c>
-      <c r="T29" s="26">
+      <c r="T29" s="21">
         <v>98195</v>
       </c>
-      <c r="U29" s="26">
+      <c r="U29" s="21">
         <v>92707</v>
       </c>
-      <c r="V29" s="26">
+      <c r="V29" s="21">
         <v>95277</v>
       </c>
-      <c r="W29" s="26">
+      <c r="W29" s="21">
         <v>100391</v>
       </c>
-      <c r="X29" s="26">
+      <c r="X29" s="21">
         <v>93121</v>
       </c>
-      <c r="Y29" s="26">
+      <c r="Y29" s="21">
         <v>93164</v>
       </c>
-      <c r="Z29" s="26">
+      <c r="Z29" s="21">
         <v>92679</v>
       </c>
-      <c r="AA29" s="26">
+      <c r="AA29" s="21">
         <v>87178</v>
       </c>
-      <c r="AB29" s="26">
+      <c r="AB29" s="21">
         <v>54421</v>
       </c>
-      <c r="AC29" s="26">
+      <c r="AC29" s="21">
         <v>91892</v>
       </c>
-      <c r="AD29" s="26">
+      <c r="AD29" s="21">
         <v>87899</v>
       </c>
-    </row>
-    <row r="30" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AE29" s="21">
+        <v>91210</v>
+      </c>
+      <c r="AF29" s="21">
+        <v>104152</v>
+      </c>
+      <c r="AG29" s="21">
+        <v>88131</v>
+      </c>
+      <c r="AH29" s="21">
+        <v>100713</v>
+      </c>
+    </row>
+    <row r="30" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>181</v>
       </c>
-      <c r="B30" s="55" t="s">
+      <c r="B30" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="C30" s="55" t="s">
+      <c r="C30" s="46" t="s">
         <v>182</v>
       </c>
-      <c r="D30" s="40" t="s">
+      <c r="D30" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="E30" s="56" t="s">
+      <c r="E30" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="F30" s="26">
+      <c r="F30" s="21">
         <v>89784</v>
       </c>
-      <c r="G30" s="26">
+      <c r="G30" s="21">
         <v>83256</v>
       </c>
-      <c r="H30" s="26">
+      <c r="H30" s="21">
         <v>100721</v>
       </c>
-      <c r="I30" s="26">
+      <c r="I30" s="21">
         <v>98055</v>
       </c>
-      <c r="J30" s="26">
+      <c r="J30" s="21">
         <v>91724</v>
       </c>
-      <c r="K30" s="26">
+      <c r="K30" s="21">
         <v>102847</v>
       </c>
-      <c r="L30" s="26">
+      <c r="L30" s="21">
         <v>93289</v>
       </c>
-      <c r="M30" s="26">
+      <c r="M30" s="21">
         <v>94539</v>
       </c>
-      <c r="N30" s="26">
+      <c r="N30" s="21">
         <v>89156</v>
       </c>
-      <c r="O30" s="26">
+      <c r="O30" s="21">
         <v>89748</v>
       </c>
-      <c r="P30" s="26">
+      <c r="P30" s="21">
         <v>81930</v>
       </c>
-      <c r="Q30" s="26">
+      <c r="Q30" s="21">
         <v>66415</v>
       </c>
-      <c r="R30" s="26">
+      <c r="R30" s="21">
         <v>92755</v>
       </c>
-      <c r="S30" s="26">
+      <c r="S30" s="21">
         <v>89917</v>
       </c>
-      <c r="T30" s="26">
+      <c r="T30" s="21">
         <v>102867</v>
       </c>
-      <c r="U30" s="26">
+      <c r="U30" s="21">
         <v>96193</v>
       </c>
-      <c r="V30" s="26">
+      <c r="V30" s="21">
         <v>98534</v>
       </c>
-      <c r="W30" s="26">
+      <c r="W30" s="21">
         <v>104382</v>
       </c>
-      <c r="X30" s="26">
+      <c r="X30" s="21">
         <v>95142</v>
       </c>
-      <c r="Y30" s="26">
+      <c r="Y30" s="21">
         <v>98580</v>
       </c>
-      <c r="Z30" s="26">
+      <c r="Z30" s="21">
         <v>95712</v>
       </c>
-      <c r="AA30" s="26">
+      <c r="AA30" s="21">
         <v>88630</v>
       </c>
-      <c r="AB30" s="26">
+      <c r="AB30" s="21">
         <v>56020</v>
       </c>
-      <c r="AC30" s="26">
+      <c r="AC30" s="21">
         <v>99073</v>
       </c>
-      <c r="AD30" s="26">
+      <c r="AD30" s="21">
         <v>90262</v>
       </c>
-    </row>
-    <row r="31" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AE30" s="21">
+        <v>95006</v>
+      </c>
+      <c r="AF30" s="21">
+        <v>107566</v>
+      </c>
+      <c r="AG30" s="21">
+        <v>91795</v>
+      </c>
+      <c r="AH30" s="21">
+        <v>104148</v>
+      </c>
+    </row>
+    <row r="31" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>183</v>
       </c>
-      <c r="B31" s="55" t="s">
+      <c r="B31" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="C31" s="55" t="s">
+      <c r="C31" s="46" t="s">
         <v>184</v>
       </c>
-      <c r="D31" s="40" t="s">
+      <c r="D31" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="E31" s="40"/>
-      <c r="F31" s="27">
+      <c r="E31" s="35"/>
+      <c r="F31" s="22">
         <v>0.12597616382432344</v>
       </c>
-      <c r="G31" s="27">
+      <c r="G31" s="22">
         <v>6.8438996082982734E-2</v>
       </c>
-      <c r="H31" s="27">
+      <c r="H31" s="22">
         <v>4.4172343181913161E-2</v>
       </c>
-      <c r="I31" s="27">
+      <c r="I31" s="22">
         <v>1.3515019784874325E-2</v>
       </c>
-      <c r="J31" s="27">
+      <c r="J31" s="22">
         <v>1.9068167240072306E-2</v>
       </c>
-      <c r="K31" s="27">
+      <c r="K31" s="22">
         <v>1.4899250839576337E-2</v>
       </c>
-      <c r="L31" s="27">
+      <c r="L31" s="22">
         <v>9.9954024554293596E-3</v>
       </c>
-      <c r="M31" s="27">
+      <c r="M31" s="22">
         <v>8.8360262175139082E-3</v>
       </c>
-      <c r="N31" s="27">
+      <c r="N31" s="22">
         <v>0</v>
       </c>
-      <c r="O31" s="27">
+      <c r="O31" s="22">
         <v>2.9830517225800622E-2</v>
       </c>
-      <c r="P31" s="27">
+      <c r="P31" s="22">
         <v>1.6429615844742788E-2</v>
       </c>
-      <c r="Q31" s="27">
+      <c r="Q31" s="22">
         <f>Q32/Q33</f>
         <v>7.6234296411574979E-3</v>
       </c>
-      <c r="R31" s="27">
+      <c r="R31" s="22">
         <f>R32/R33</f>
         <v>2.2019664072101598E-3</v>
       </c>
-      <c r="S31" s="27">
+      <c r="S31" s="22">
         <f>S32/S33</f>
         <v>2.6622383029535836E-3</v>
       </c>
-      <c r="T31" s="27">
+      <c r="T31" s="22">
         <f>T32/T33</f>
         <v>6.4293117947313873E-4</v>
       </c>
-      <c r="U31" s="27">
+      <c r="U31" s="22">
         <f t="shared" ref="U31:W31" si="9">U32/U33</f>
         <v>2.4254435244803953E-4</v>
       </c>
-      <c r="V31" s="27">
+      <c r="V31" s="22">
         <f t="shared" si="9"/>
         <v>5.0142194282293067E-4</v>
       </c>
-      <c r="W31" s="27">
+      <c r="W31" s="22">
         <f t="shared" si="9"/>
         <v>4.1266382753953323E-5</v>
       </c>
-      <c r="X31" s="27">
+      <c r="X31" s="22">
         <v>1.2390408331131424E-4</v>
       </c>
-      <c r="Y31" s="27">
+      <c r="Y31" s="22">
         <v>0</v>
       </c>
-      <c r="Z31" s="27">
+      <c r="Z31" s="22">
         <v>0</v>
       </c>
-      <c r="AA31" s="27">
+      <c r="AA31" s="22">
         <v>1.6122121049812532E-2</v>
       </c>
-      <c r="AB31" s="27">
+      <c r="AB31" s="22">
         <v>0</v>
       </c>
-      <c r="AC31" s="27">
+      <c r="AC31" s="22">
         <v>0</v>
       </c>
-      <c r="AD31" s="27">
+      <c r="AD31" s="22">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AE31" s="22">
+        <v>1.4029786315562271E-3</v>
+      </c>
+      <c r="AF31" s="22">
+        <v>7.0197996576978876E-3</v>
+      </c>
+      <c r="AG31" s="22">
+        <v>1.1661291155870132E-3</v>
+      </c>
+      <c r="AH31" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>185</v>
       </c>
-      <c r="B32" s="55" t="s">
+      <c r="B32" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="C32" s="55" t="s">
+      <c r="C32" s="46" t="s">
         <v>186</v>
       </c>
-      <c r="D32" s="40" t="s">
+      <c r="D32" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="E32" s="56" t="s">
+      <c r="E32" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="F32" s="26">
+      <c r="F32" s="21">
         <v>9566</v>
       </c>
-      <c r="G32" s="26">
+      <c r="G32" s="21">
         <v>5661</v>
       </c>
-      <c r="H32" s="26">
+      <c r="H32" s="21">
         <v>4228</v>
       </c>
-      <c r="I32" s="26">
+      <c r="I32" s="21">
         <v>1455</v>
       </c>
-      <c r="J32" s="26">
+      <c r="J32" s="21">
         <v>2289</v>
       </c>
-      <c r="K32" s="26">
+      <c r="K32" s="21">
         <v>2307</v>
       </c>
-      <c r="L32" s="26">
+      <c r="L32" s="21">
         <v>1761</v>
       </c>
-      <c r="M32" s="26">
+      <c r="M32" s="21">
         <v>1855</v>
       </c>
-      <c r="N32" s="26">
+      <c r="N32" s="21">
         <v>0</v>
       </c>
-      <c r="O32" s="26">
+      <c r="O32" s="21">
         <v>2311</v>
       </c>
-      <c r="P32" s="26">
+      <c r="P32" s="21">
         <v>2472</v>
       </c>
-      <c r="Q32" s="26">
+      <c r="Q32" s="21">
         <v>1352</v>
       </c>
-      <c r="R32" s="26">
+      <c r="R32" s="21">
         <v>516</v>
       </c>
-      <c r="S32" s="26">
+      <c r="S32" s="21">
         <v>816</v>
       </c>
-      <c r="T32" s="26">
+      <c r="T32" s="21">
         <v>263</v>
       </c>
-      <c r="U32" s="26">
+      <c r="U32" s="21">
         <v>117</v>
       </c>
-      <c r="V32" s="26">
+      <c r="V32" s="21">
         <v>268</v>
       </c>
-      <c r="W32" s="26">
+      <c r="W32" s="21">
         <v>25</v>
       </c>
-      <c r="X32" s="26">
+      <c r="X32" s="21">
         <v>83</v>
       </c>
-      <c r="Y32" s="26">
+      <c r="Y32" s="21">
         <v>0</v>
       </c>
-      <c r="Z32" s="26">
+      <c r="Z32" s="21">
         <v>0</v>
       </c>
-      <c r="AA32" s="26">
+      <c r="AA32" s="21">
         <v>301</v>
       </c>
-      <c r="AB32" s="26">
+      <c r="AB32" s="21">
         <v>0</v>
       </c>
-      <c r="AC32" s="26">
+      <c r="AC32" s="21">
         <v>0</v>
       </c>
-      <c r="AD32" s="26">
+      <c r="AD32" s="21">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AE32" s="21">
+        <v>130</v>
+      </c>
+      <c r="AF32" s="21">
+        <v>808</v>
+      </c>
+      <c r="AG32" s="21">
+        <v>158</v>
+      </c>
+      <c r="AH32" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>187</v>
       </c>
-      <c r="B33" s="55" t="s">
+      <c r="B33" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="C33" s="55" t="s">
+      <c r="C33" s="46" t="s">
         <v>188</v>
       </c>
-      <c r="D33" s="40" t="s">
+      <c r="D33" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="E33" s="56" t="s">
+      <c r="E33" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="F33" s="26">
+      <c r="F33" s="21">
         <v>75935</v>
       </c>
-      <c r="G33" s="26">
+      <c r="G33" s="21">
         <v>82716</v>
       </c>
-      <c r="H33" s="26">
+      <c r="H33" s="21">
         <v>95716</v>
       </c>
-      <c r="I33" s="26">
+      <c r="I33" s="21">
         <v>107658</v>
       </c>
-      <c r="J33" s="26">
+      <c r="J33" s="21">
         <v>120043</v>
       </c>
-      <c r="K33" s="26">
+      <c r="K33" s="21">
         <v>154840</v>
       </c>
-      <c r="L33" s="26">
+      <c r="L33" s="21">
         <v>176181</v>
       </c>
-      <c r="M33" s="26">
+      <c r="M33" s="21">
         <v>209936</v>
       </c>
-      <c r="N33" s="26">
+      <c r="N33" s="21">
         <v>209936</v>
       </c>
-      <c r="O33" s="26">
+      <c r="O33" s="21">
         <v>77471</v>
       </c>
-      <c r="P33" s="26">
+      <c r="P33" s="21">
         <v>150460</v>
       </c>
-      <c r="Q33" s="26">
+      <c r="Q33" s="21">
         <v>177348</v>
       </c>
-      <c r="R33" s="26">
+      <c r="R33" s="21">
         <v>234336</v>
       </c>
-      <c r="S33" s="26">
+      <c r="S33" s="21">
         <v>306509</v>
       </c>
-      <c r="T33" s="26">
+      <c r="T33" s="21">
         <v>409064</v>
       </c>
-      <c r="U33" s="26">
+      <c r="U33" s="21">
         <v>482386</v>
       </c>
-      <c r="V33" s="26">
+      <c r="V33" s="21">
         <v>534480</v>
       </c>
-      <c r="W33" s="26">
+      <c r="W33" s="21">
         <v>605820</v>
       </c>
-      <c r="X33" s="26">
+      <c r="X33" s="21">
         <v>669873</v>
       </c>
-      <c r="Y33" s="26">
+      <c r="Y33" s="21">
         <v>772403</v>
       </c>
-      <c r="Z33" s="26">
+      <c r="Z33" s="21">
         <v>106006</v>
       </c>
-      <c r="AA33" s="26">
+      <c r="AA33" s="21">
         <v>18670</v>
       </c>
-      <c r="AB33" s="26">
+      <c r="AB33" s="21">
         <v>37183</v>
       </c>
-      <c r="AC33" s="26">
+      <c r="AC33" s="21">
         <v>50128</v>
       </c>
-      <c r="AD33" s="26">
+      <c r="AD33" s="21">
         <v>76281</v>
       </c>
-    </row>
-    <row r="34" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AE33" s="21">
+        <v>92660</v>
+      </c>
+      <c r="AF33" s="21">
+        <v>115103</v>
+      </c>
+      <c r="AG33" s="21">
+        <v>135491</v>
+      </c>
+      <c r="AH33" s="21">
+        <v>152850</v>
+      </c>
+    </row>
+    <row r="34" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>189</v>
       </c>
-      <c r="B34" s="55" t="s">
+      <c r="B34" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="C34" s="55" t="s">
+      <c r="C34" s="46" t="s">
         <v>190</v>
       </c>
-      <c r="D34" s="40" t="s">
+      <c r="D34" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="E34" s="40"/>
-      <c r="F34" s="26"/>
-      <c r="G34" s="26"/>
-      <c r="H34" s="26"/>
-      <c r="I34" s="26"/>
-      <c r="J34" s="26"/>
-      <c r="K34" s="26"/>
-      <c r="L34" s="26"/>
-      <c r="M34" s="26"/>
-      <c r="N34" s="38">
+      <c r="E34" s="35"/>
+      <c r="F34" s="21"/>
+      <c r="G34" s="21"/>
+      <c r="H34" s="21"/>
+      <c r="I34" s="21"/>
+      <c r="J34" s="21"/>
+      <c r="K34" s="21"/>
+      <c r="L34" s="21"/>
+      <c r="M34" s="21"/>
+      <c r="N34" s="33">
         <f>N35/N36</f>
         <v>8.5959096002988414E-2</v>
       </c>
-      <c r="O34" s="38">
+      <c r="O34" s="33">
         <f t="shared" ref="O34:Q34" si="10">O35/O36</f>
         <v>8.3806588770414803E-2</v>
       </c>
-      <c r="P34" s="38">
+      <c r="P34" s="33">
         <f t="shared" si="10"/>
         <v>0.13360461134134469</v>
       </c>
-      <c r="Q34" s="38">
+      <c r="Q34" s="33">
         <f t="shared" si="10"/>
         <v>5.7919455819419319E-2</v>
       </c>
-      <c r="R34" s="38">
+      <c r="R34" s="33">
         <f>R35/R36</f>
         <v>0.04</v>
       </c>
-      <c r="S34" s="38">
+      <c r="S34" s="33">
         <f>S35/S36</f>
         <v>2.9309630426565089E-2</v>
       </c>
-      <c r="T34" s="38">
+      <c r="T34" s="33">
         <f>T35/T36</f>
         <v>2.7305488819072261E-2</v>
       </c>
-      <c r="U34" s="38">
+      <c r="U34" s="33">
         <f t="shared" ref="U34:W34" si="11">U35/U36</f>
         <v>3.3333333333333333E-2</v>
       </c>
-      <c r="V34" s="38">
+      <c r="V34" s="33">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="W34" s="38">
+      <c r="W34" s="33">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="X34" s="38"/>
-      <c r="Y34" s="27"/>
-      <c r="Z34" s="27"/>
-      <c r="AA34" s="27"/>
-      <c r="AB34" s="27"/>
-      <c r="AC34" s="27"/>
-      <c r="AD34" s="27"/>
-    </row>
-    <row r="35" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="X34" s="33"/>
+      <c r="Y34" s="22"/>
+      <c r="Z34" s="22"/>
+      <c r="AA34" s="22"/>
+      <c r="AB34" s="22"/>
+      <c r="AC34" s="22"/>
+      <c r="AD34" s="22"/>
+      <c r="AE34" s="22"/>
+      <c r="AF34" s="22"/>
+      <c r="AG34" s="22"/>
+      <c r="AH34" s="22"/>
+    </row>
+    <row r="35" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>191</v>
       </c>
-      <c r="B35" s="55" t="s">
+      <c r="B35" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="C35" s="55" t="s">
+      <c r="C35" s="46" t="s">
         <v>192</v>
       </c>
-      <c r="D35" s="40" t="s">
+      <c r="D35" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="E35" s="57" t="s">
+      <c r="E35" s="48" t="s">
         <v>193</v>
       </c>
-      <c r="F35" s="39"/>
-      <c r="G35" s="40"/>
-      <c r="H35" s="40"/>
-      <c r="I35" s="40"/>
-      <c r="J35" s="40"/>
-      <c r="K35" s="40"/>
-      <c r="L35" s="40"/>
-      <c r="M35" s="41"/>
-      <c r="N35" s="26">
+      <c r="F35" s="34"/>
+      <c r="G35" s="35"/>
+      <c r="H35" s="35"/>
+      <c r="I35" s="35"/>
+      <c r="J35" s="35"/>
+      <c r="K35" s="35"/>
+      <c r="L35" s="35"/>
+      <c r="M35" s="36"/>
+      <c r="N35" s="21">
         <v>25772600</v>
       </c>
-      <c r="O35" s="26">
+      <c r="O35" s="21">
         <v>66108900</v>
       </c>
-      <c r="P35" s="26">
+      <c r="P35" s="21">
         <v>17360650</v>
       </c>
-      <c r="Q35" s="26">
+      <c r="Q35" s="21">
         <v>7220500</v>
       </c>
-      <c r="R35" s="26">
+      <c r="R35" s="21">
         <v>2321200</v>
       </c>
-      <c r="S35" s="26">
+      <c r="S35" s="21">
         <v>8063900</v>
       </c>
-      <c r="T35" s="26">
+      <c r="T35" s="21">
         <v>2364000</v>
       </c>
-      <c r="U35" s="26">
+      <c r="U35" s="21">
         <v>4157150</v>
       </c>
-      <c r="V35" s="48">
+      <c r="V35" s="43">
         <v>0</v>
       </c>
-      <c r="W35" s="48">
+      <c r="W35" s="43">
         <v>0</v>
       </c>
-      <c r="X35" s="48"/>
-      <c r="Y35" s="26"/>
-      <c r="Z35" s="26"/>
-      <c r="AA35" s="26"/>
-      <c r="AB35" s="26"/>
-      <c r="AC35" s="26"/>
-      <c r="AD35" s="26"/>
-    </row>
-    <row r="36" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="X35" s="43"/>
+      <c r="Y35" s="21"/>
+      <c r="Z35" s="21"/>
+      <c r="AA35" s="21"/>
+      <c r="AB35" s="21"/>
+      <c r="AC35" s="21"/>
+      <c r="AD35" s="21"/>
+      <c r="AE35" s="21"/>
+      <c r="AF35" s="21"/>
+      <c r="AG35" s="21"/>
+      <c r="AH35" s="21"/>
+    </row>
+    <row r="36" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>194</v>
       </c>
-      <c r="B36" s="55" t="s">
+      <c r="B36" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="C36" s="55" t="s">
+      <c r="C36" s="46" t="s">
         <v>195</v>
       </c>
-      <c r="D36" s="40" t="s">
+      <c r="D36" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="E36" s="57" t="s">
+      <c r="E36" s="48" t="s">
         <v>193</v>
       </c>
-      <c r="F36" s="39"/>
-      <c r="G36" s="40"/>
-      <c r="H36" s="40"/>
-      <c r="I36" s="40"/>
-      <c r="J36" s="40"/>
-      <c r="K36" s="40"/>
-      <c r="L36" s="40"/>
-      <c r="M36" s="41"/>
-      <c r="N36" s="26">
+      <c r="F36" s="34"/>
+      <c r="G36" s="35"/>
+      <c r="H36" s="35"/>
+      <c r="I36" s="35"/>
+      <c r="J36" s="35"/>
+      <c r="K36" s="35"/>
+      <c r="L36" s="35"/>
+      <c r="M36" s="36"/>
+      <c r="N36" s="21">
         <v>299824000</v>
       </c>
-      <c r="O36" s="26">
+      <c r="O36" s="21">
         <v>788827000</v>
       </c>
-      <c r="P36" s="26">
+      <c r="P36" s="21">
         <v>129940500</v>
       </c>
-      <c r="Q36" s="26">
+      <c r="Q36" s="21">
         <v>124664500</v>
       </c>
-      <c r="R36" s="26">
+      <c r="R36" s="21">
         <v>58030000</v>
       </c>
-      <c r="S36" s="26">
+      <c r="S36" s="21">
         <v>275128000</v>
       </c>
-      <c r="T36" s="26">
+      <c r="T36" s="21">
         <v>86576000</v>
       </c>
-      <c r="U36" s="26">
+      <c r="U36" s="21">
         <v>124714500</v>
       </c>
-      <c r="V36" s="26">
+      <c r="V36" s="21">
         <v>47538000</v>
       </c>
-      <c r="W36" s="26">
+      <c r="W36" s="21">
         <v>27067000</v>
       </c>
-      <c r="X36" s="49"/>
-      <c r="Y36" s="26"/>
-      <c r="Z36" s="26"/>
-      <c r="AA36" s="26"/>
-      <c r="AB36" s="26"/>
-      <c r="AC36" s="26"/>
-      <c r="AD36" s="26"/>
-    </row>
-    <row r="37" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="X36" s="44"/>
+      <c r="Y36" s="21"/>
+      <c r="Z36" s="21"/>
+      <c r="AA36" s="21"/>
+      <c r="AB36" s="21"/>
+      <c r="AC36" s="21"/>
+      <c r="AD36" s="21"/>
+      <c r="AE36" s="21"/>
+      <c r="AF36" s="21"/>
+      <c r="AG36" s="21"/>
+      <c r="AH36" s="21"/>
+    </row>
+    <row r="37" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>196</v>
       </c>
-      <c r="B37" s="55" t="s">
+      <c r="B37" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="C37" s="55" t="s">
+      <c r="C37" s="46" t="s">
         <v>197</v>
       </c>
-      <c r="D37" s="40" t="s">
+      <c r="D37" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="E37" s="57" t="s">
+      <c r="E37" s="48" t="s">
         <v>193</v>
       </c>
-      <c r="F37" s="39"/>
-      <c r="G37" s="40"/>
-      <c r="H37" s="40"/>
-      <c r="I37" s="40"/>
-      <c r="J37" s="40"/>
-      <c r="K37" s="40"/>
-      <c r="L37" s="40"/>
-      <c r="M37" s="41"/>
-      <c r="N37" s="26">
+      <c r="F37" s="34"/>
+      <c r="G37" s="35"/>
+      <c r="H37" s="35"/>
+      <c r="I37" s="35"/>
+      <c r="J37" s="35"/>
+      <c r="K37" s="35"/>
+      <c r="L37" s="35"/>
+      <c r="M37" s="36"/>
+      <c r="N37" s="21">
         <v>24</v>
       </c>
-      <c r="O37" s="26">
+      <c r="O37" s="21">
         <v>60</v>
       </c>
-      <c r="P37" s="26">
+      <c r="P37" s="21">
         <v>17</v>
       </c>
-      <c r="Q37" s="26">
+      <c r="Q37" s="21">
         <v>13</v>
       </c>
-      <c r="R37" s="26">
+      <c r="R37" s="21">
         <v>5</v>
       </c>
-      <c r="S37" s="26">
+      <c r="S37" s="21">
         <v>13</v>
       </c>
-      <c r="T37" s="26">
+      <c r="T37" s="21">
         <v>8</v>
       </c>
-      <c r="U37" s="26">
+      <c r="U37" s="21">
         <v>9</v>
       </c>
-      <c r="V37" s="26">
+      <c r="V37" s="21">
         <v>6</v>
       </c>
-      <c r="W37" s="26">
+      <c r="W37" s="21">
         <v>2</v>
       </c>
-      <c r="X37" s="50"/>
-      <c r="Y37" s="26"/>
-      <c r="Z37" s="26"/>
-      <c r="AA37" s="26"/>
-      <c r="AB37" s="26"/>
-      <c r="AC37" s="26"/>
-      <c r="AD37" s="26"/>
-    </row>
-    <row r="38" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="X37" s="45"/>
+      <c r="Y37" s="21"/>
+      <c r="Z37" s="21"/>
+      <c r="AA37" s="21"/>
+      <c r="AB37" s="21"/>
+      <c r="AC37" s="21"/>
+      <c r="AD37" s="21"/>
+      <c r="AE37" s="21"/>
+      <c r="AF37" s="21"/>
+      <c r="AG37" s="21"/>
+      <c r="AH37" s="21"/>
+    </row>
+    <row r="38" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>198</v>
       </c>
-      <c r="B38" s="55" t="s">
+      <c r="B38" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="C38" s="55" t="s">
+      <c r="C38" s="46" t="s">
         <v>199</v>
       </c>
-      <c r="D38" s="40" t="s">
+      <c r="D38" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="E38" s="40"/>
-      <c r="F38" s="40"/>
-      <c r="G38" s="40"/>
-      <c r="H38" s="40"/>
-      <c r="I38" s="40"/>
-      <c r="J38" s="40"/>
-      <c r="K38" s="40"/>
-      <c r="L38" s="40"/>
-      <c r="M38" s="40"/>
-      <c r="N38" s="42">
+      <c r="E38" s="35"/>
+      <c r="F38" s="35"/>
+      <c r="G38" s="35"/>
+      <c r="H38" s="35"/>
+      <c r="I38" s="35"/>
+      <c r="J38" s="35"/>
+      <c r="K38" s="35"/>
+      <c r="L38" s="35"/>
+      <c r="M38" s="35"/>
+      <c r="N38" s="37">
         <f>N39/N40</f>
         <v>0.30205320541459935</v>
       </c>
-      <c r="O38" s="42">
+      <c r="O38" s="37">
         <f t="shared" ref="O38:Q38" si="12">O39/O40</f>
         <v>0.16678314329701199</v>
       </c>
-      <c r="P38" s="42">
+      <c r="P38" s="37">
         <f t="shared" si="12"/>
         <v>0.16345199611718877</v>
       </c>
-      <c r="Q38" s="42">
+      <c r="Q38" s="37">
         <f t="shared" si="12"/>
         <v>0.11897059274477936</v>
       </c>
-      <c r="R38" s="42"/>
-      <c r="S38" s="42"/>
-      <c r="T38" s="42"/>
-      <c r="U38" s="42"/>
-      <c r="V38" s="42"/>
-      <c r="W38" s="42"/>
-      <c r="X38" s="42"/>
-      <c r="Y38" s="27"/>
-      <c r="Z38" s="27"/>
-      <c r="AA38" s="27"/>
-      <c r="AB38" s="27"/>
-      <c r="AC38" s="27"/>
-      <c r="AD38" s="27"/>
-    </row>
-    <row r="39" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="R38" s="37"/>
+      <c r="S38" s="37"/>
+      <c r="T38" s="37"/>
+      <c r="U38" s="37"/>
+      <c r="V38" s="37"/>
+      <c r="W38" s="37"/>
+      <c r="X38" s="37"/>
+      <c r="Y38" s="22"/>
+      <c r="Z38" s="22"/>
+      <c r="AA38" s="22"/>
+      <c r="AB38" s="22"/>
+      <c r="AC38" s="22"/>
+      <c r="AD38" s="22"/>
+      <c r="AE38" s="22"/>
+      <c r="AF38" s="22"/>
+      <c r="AG38" s="22"/>
+      <c r="AH38" s="22"/>
+    </row>
+    <row r="39" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>200</v>
       </c>
-      <c r="B39" s="55" t="s">
+      <c r="B39" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="C39" s="55" t="s">
+      <c r="C39" s="46" t="s">
         <v>201</v>
       </c>
-      <c r="D39" s="40" t="s">
+      <c r="D39" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="E39" s="57" t="s">
+      <c r="E39" s="48" t="s">
         <v>202</v>
       </c>
-      <c r="F39" s="40"/>
-      <c r="G39" s="40"/>
-      <c r="H39" s="40"/>
-      <c r="I39" s="40"/>
-      <c r="J39" s="40"/>
-      <c r="K39" s="40"/>
-      <c r="L39" s="40"/>
-      <c r="M39" s="40"/>
-      <c r="N39" s="43">
+      <c r="F39" s="35"/>
+      <c r="G39" s="35"/>
+      <c r="H39" s="35"/>
+      <c r="I39" s="35"/>
+      <c r="J39" s="35"/>
+      <c r="K39" s="35"/>
+      <c r="L39" s="35"/>
+      <c r="M39" s="35"/>
+      <c r="N39" s="38">
         <v>308290</v>
       </c>
-      <c r="O39" s="43">
+      <c r="O39" s="38">
         <v>195216</v>
       </c>
-      <c r="P39" s="43">
+      <c r="P39" s="38">
         <v>195832</v>
       </c>
-      <c r="Q39" s="43">
+      <c r="Q39" s="38">
         <v>77595</v>
       </c>
-      <c r="R39" s="43"/>
-      <c r="S39" s="43"/>
-      <c r="T39" s="43"/>
-      <c r="U39" s="43"/>
-      <c r="V39" s="43"/>
-      <c r="W39" s="43"/>
-      <c r="X39" s="43"/>
-      <c r="Y39" s="26"/>
-      <c r="Z39" s="26"/>
-      <c r="AA39" s="26"/>
-      <c r="AB39" s="26"/>
-      <c r="AC39" s="26"/>
-      <c r="AD39" s="26"/>
-    </row>
-    <row r="40" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="R39" s="38"/>
+      <c r="S39" s="38"/>
+      <c r="T39" s="38"/>
+      <c r="U39" s="38"/>
+      <c r="V39" s="38"/>
+      <c r="W39" s="38"/>
+      <c r="X39" s="38"/>
+      <c r="Y39" s="21"/>
+      <c r="Z39" s="21"/>
+      <c r="AA39" s="21"/>
+      <c r="AB39" s="21"/>
+      <c r="AC39" s="21"/>
+      <c r="AD39" s="21"/>
+      <c r="AE39" s="21"/>
+      <c r="AF39" s="21"/>
+      <c r="AG39" s="21"/>
+      <c r="AH39" s="21"/>
+    </row>
+    <row r="40" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>203</v>
       </c>
-      <c r="B40" s="55" t="s">
+      <c r="B40" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="C40" s="55" t="s">
+      <c r="C40" s="46" t="s">
         <v>204</v>
       </c>
-      <c r="D40" s="40" t="s">
+      <c r="D40" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="E40" s="57" t="s">
+      <c r="E40" s="48" t="s">
         <v>202</v>
       </c>
-      <c r="F40" s="40"/>
-      <c r="G40" s="40"/>
-      <c r="H40" s="40"/>
-      <c r="I40" s="40"/>
-      <c r="J40" s="40"/>
-      <c r="K40" s="40"/>
-      <c r="L40" s="40"/>
-      <c r="M40" s="40"/>
-      <c r="N40" s="26">
+      <c r="F40" s="35"/>
+      <c r="G40" s="35"/>
+      <c r="H40" s="35"/>
+      <c r="I40" s="35"/>
+      <c r="J40" s="35"/>
+      <c r="K40" s="35"/>
+      <c r="L40" s="35"/>
+      <c r="M40" s="35"/>
+      <c r="N40" s="21">
         <v>1020648</v>
       </c>
-      <c r="O40" s="26">
+      <c r="O40" s="21">
         <v>1170478</v>
       </c>
-      <c r="P40" s="26">
+      <c r="P40" s="21">
         <v>1198101</v>
       </c>
-      <c r="Q40" s="26">
+      <c r="Q40" s="21">
         <v>652220</v>
       </c>
-      <c r="R40" s="26"/>
-      <c r="S40" s="26"/>
-      <c r="T40" s="26"/>
-      <c r="U40" s="26"/>
-      <c r="V40" s="26"/>
-      <c r="W40" s="26"/>
-      <c r="X40" s="26"/>
-      <c r="Y40" s="26"/>
-      <c r="Z40" s="26"/>
-      <c r="AA40" s="26"/>
-      <c r="AB40" s="26"/>
-      <c r="AC40" s="26"/>
-      <c r="AD40" s="26"/>
+      <c r="R40" s="21"/>
+      <c r="S40" s="21"/>
+      <c r="T40" s="21"/>
+      <c r="U40" s="21"/>
+      <c r="V40" s="21"/>
+      <c r="W40" s="21"/>
+      <c r="X40" s="21"/>
+      <c r="Y40" s="21"/>
+      <c r="Z40" s="21"/>
+      <c r="AA40" s="21"/>
+      <c r="AB40" s="21"/>
+      <c r="AC40" s="21"/>
+      <c r="AD40" s="21"/>
+      <c r="AE40" s="21"/>
+      <c r="AF40" s="21"/>
+      <c r="AG40" s="21"/>
+      <c r="AH40" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A4:Q4"/>
-    <mergeCell ref="A1:AD1"/>
-    <mergeCell ref="F2:AD2"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="E2:E3"/>
+    <mergeCell ref="A1:AH1"/>
+    <mergeCell ref="F2:AH2"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5:Q22">
-    <cfRule type="expression" dxfId="19" priority="20" stopIfTrue="1">
+  <conditionalFormatting sqref="B5:E40">
+    <cfRule type="expression" dxfId="21" priority="10" stopIfTrue="1">
       <formula>$D5="Pembentuk"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:Q22">
-    <cfRule type="expression" dxfId="18" priority="19" stopIfTrue="1">
+  <conditionalFormatting sqref="B5:Q40">
+    <cfRule type="expression" dxfId="20" priority="9" stopIfTrue="1">
       <formula>$D5="Hasil"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F23:Q40">
-    <cfRule type="expression" dxfId="17" priority="17" stopIfTrue="1">
-      <formula>$D23="Hasil"</formula>
+  <conditionalFormatting sqref="F5:Y22">
+    <cfRule type="expression" dxfId="19" priority="24" stopIfTrue="1">
+      <formula>$D5="Pembentuk"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="18" stopIfTrue="1">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F23:AD40">
+    <cfRule type="expression" dxfId="18" priority="16" stopIfTrue="1">
       <formula>$D23="Pembentuk"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R5:Y22 Z9:AA10 Z12:AA13 Z17:AA22">
-    <cfRule type="expression" dxfId="15" priority="16" stopIfTrue="1">
-      <formula>$D5="Pembentuk"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="R5:Y22">
-    <cfRule type="expression" dxfId="14" priority="15" stopIfTrue="1">
+    <cfRule type="expression" dxfId="17" priority="23" stopIfTrue="1">
       <formula>$D5="Hasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R23:AD40">
-    <cfRule type="expression" dxfId="13" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="16" priority="15" stopIfTrue="1">
       <formula>$D23="Hasil"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="12" priority="8" stopIfTrue="1">
-      <formula>$D23="Pembentuk"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y9:AD10 Y12:AD13 Y17:AD22">
-    <cfRule type="expression" dxfId="11" priority="11" stopIfTrue="1">
+    <cfRule type="expression" dxfId="15" priority="19" stopIfTrue="1">
       <formula>$D9="Hasil"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z5:AD8">
-    <cfRule type="expression" dxfId="10" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="14" priority="13" stopIfTrue="1">
       <formula>$D5="Hasil"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="13" priority="14" stopIfTrue="1">
       <formula>$D5="Pembentuk"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z11:AD11">
-    <cfRule type="expression" dxfId="8" priority="13" stopIfTrue="1">
+  <conditionalFormatting sqref="Z9:AD10 Z12:AD13 Z17:AD22">
+    <cfRule type="expression" dxfId="12" priority="20" stopIfTrue="1">
+      <formula>$D9="Pembentuk"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z11:AH11">
+    <cfRule type="expression" dxfId="11" priority="21" stopIfTrue="1">
       <formula>$D11="Hasil"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="14" stopIfTrue="1">
+    <cfRule type="expression" dxfId="10" priority="22" stopIfTrue="1">
       <formula>$D11="Pembentuk"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z14:AD16">
-    <cfRule type="expression" dxfId="6" priority="9" stopIfTrue="1">
+    <cfRule type="expression" dxfId="9" priority="17" stopIfTrue="1">
       <formula>$D14="Hasil"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="10" stopIfTrue="1">
+    <cfRule type="expression" dxfId="8" priority="18" stopIfTrue="1">
       <formula>$D14="Pembentuk"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB9:AD10 AB12:AD13 AB17:AD22">
-    <cfRule type="expression" dxfId="4" priority="12" stopIfTrue="1">
+  <conditionalFormatting sqref="AE23:AH40">
+    <cfRule type="expression" dxfId="7" priority="4" stopIfTrue="1">
+      <formula>$D23="Pembentuk"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE23:AH40">
+    <cfRule type="expression" dxfId="6" priority="3" stopIfTrue="1">
+      <formula>$D23="Hasil"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE9:AH10 AE12:AH13 AE17:AH22">
+    <cfRule type="expression" dxfId="5" priority="7" stopIfTrue="1">
+      <formula>$D9="Hasil"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE5:AH8">
+    <cfRule type="expression" dxfId="4" priority="1" stopIfTrue="1">
+      <formula>$D5="Hasil"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="2" stopIfTrue="1">
+      <formula>$D5="Pembentuk"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE9:AH10 AE12:AH13 AE17:AH22">
+    <cfRule type="expression" dxfId="2" priority="8" stopIfTrue="1">
       <formula>$D9="Pembentuk"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B5:E22">
-    <cfRule type="expression" dxfId="3" priority="4" stopIfTrue="1">
-      <formula>$D5="Pembentuk"</formula>
+  <conditionalFormatting sqref="AE14:AH16">
+    <cfRule type="expression" dxfId="1" priority="5" stopIfTrue="1">
+      <formula>$D14="Hasil"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B5:E22">
-    <cfRule type="expression" dxfId="2" priority="3" stopIfTrue="1">
-      <formula>$D5="Hasil"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B23:E40">
-    <cfRule type="expression" dxfId="1" priority="1" stopIfTrue="1">
-      <formula>$D23="Hasil"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="2" stopIfTrue="1">
-      <formula>$D23="Pembentuk"</formula>
+    <cfRule type="expression" dxfId="0" priority="6" stopIfTrue="1">
+      <formula>$D14="Pembentuk"</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
@@ -5387,7 +5728,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="52" customWidth="1"/>
@@ -5399,31 +5740,31 @@
     <col min="8" max="8" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="54" t="s">
         <v>99</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-    </row>
-    <row r="2" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="21" t="s">
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+    </row>
+    <row r="2" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="58" t="s">
         <v>100</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-    </row>
-    <row r="3" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="58"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
+    </row>
+    <row r="3" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>101</v>
       </c>
@@ -5449,7 +5790,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>109</v>
       </c>
@@ -5475,7 +5816,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="24" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>117</v>
       </c>
@@ -5501,7 +5842,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="24" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>125</v>
       </c>
@@ -5527,7 +5868,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="24" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>132</v>
       </c>
@@ -5553,7 +5894,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="24" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
         <v>138</v>
       </c>
@@ -5579,7 +5920,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="24" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>144</v>
       </c>
@@ -5605,7 +5946,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="24" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>148</v>
       </c>
@@ -5631,7 +5972,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="24" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>154</v>
       </c>
@@ -5657,7 +5998,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="24" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>160</v>
       </c>
@@ -5683,7 +6024,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>166</v>
       </c>
@@ -5709,7 +6050,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="24" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
         <v>170</v>
       </c>
